--- a/research/traditional_assets/database/data/serbia/serbia_household_products.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_household_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1022801005380828</v>
+        <v>0.1021649303872757</v>
       </c>
       <c r="C2">
-        <v>47.76807319934465</v>
+        <v>47.33235732279788</v>
       </c>
       <c r="D2">
-        <v>41.69807319934465</v>
+        <v>41.72935732279787</v>
       </c>
       <c r="E2">
-        <v>-12.5</v>
+        <v>-12.033</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="G2">
         <v>6.07</v>
@@ -1451,28 +1451,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0234901</v>
       </c>
       <c r="N2">
-        <v>8.450000000000001</v>
+        <v>8.426509900000001</v>
       </c>
       <c r="O2">
-        <v>1.2675</v>
+        <v>1.263976485</v>
       </c>
       <c r="P2">
-        <v>7.182500000000001</v>
+        <v>7.162533415</v>
       </c>
       <c r="Q2">
-        <v>11.5325</v>
+        <v>11.512533415</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1022801005380828</v>
+        <v>0.1027650306942179</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6824263892259379</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>359.7260122349415</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1021649303872757</v>
+        <v>0.1020497602364686</v>
       </c>
       <c r="C3">
-        <v>47.33235732279788</v>
+        <v>46.89668842353933</v>
       </c>
       <c r="D3">
-        <v>41.72935732279787</v>
+        <v>41.76068842353933</v>
       </c>
       <c r="E3">
-        <v>-12.033</v>
+        <v>-11.566</v>
       </c>
       <c r="F3">
-        <v>0.467</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G3">
         <v>6.07</v>
@@ -1533,28 +1533,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M3">
-        <v>0.0234901</v>
+        <v>0.0469802</v>
       </c>
       <c r="N3">
-        <v>8.426509900000001</v>
+        <v>8.403019800000001</v>
       </c>
       <c r="O3">
-        <v>1.263976485</v>
+        <v>1.26045297</v>
       </c>
       <c r="P3">
-        <v>7.162533415</v>
+        <v>7.142566830000001</v>
       </c>
       <c r="Q3">
-        <v>11.512533415</v>
+        <v>11.49256683</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1027650306942179</v>
+        <v>0.1032598573841516</v>
       </c>
       <c r="T3">
-        <v>0.6824263892259379</v>
+        <v>0.6883542854666466</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>359.7260122349415</v>
+        <v>179.8630061174708</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1020497602364686</v>
+        <v>0.1019345900856614</v>
       </c>
       <c r="C4">
-        <v>46.89668842353933</v>
+        <v>46.46106660746254</v>
       </c>
       <c r="D4">
-        <v>41.76068842353933</v>
+        <v>41.79206660746254</v>
       </c>
       <c r="E4">
-        <v>-11.566</v>
+        <v>-11.099</v>
       </c>
       <c r="F4">
-        <v>0.9340000000000001</v>
+        <v>1.401</v>
       </c>
       <c r="G4">
         <v>6.07</v>
@@ -1615,28 +1615,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M4">
-        <v>0.0469802</v>
+        <v>0.0704703</v>
       </c>
       <c r="N4">
-        <v>8.403019800000001</v>
+        <v>8.379529700000001</v>
       </c>
       <c r="O4">
-        <v>1.26045297</v>
+        <v>1.256929455</v>
       </c>
       <c r="P4">
-        <v>7.142566830000001</v>
+        <v>7.122600245000001</v>
       </c>
       <c r="Q4">
-        <v>11.49256683</v>
+        <v>11.472600245</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1032598573841516</v>
+        <v>0.1037648866862489</v>
       </c>
       <c r="T4">
-        <v>0.6883542854666466</v>
+        <v>0.6944044063721118</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>179.8630061174708</v>
+        <v>119.9086707449805</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1019345900856614</v>
+        <v>0.1018194199348543</v>
       </c>
       <c r="C5">
-        <v>46.46106660746254</v>
+        <v>46.02549198077951</v>
       </c>
       <c r="D5">
-        <v>41.79206660746254</v>
+        <v>41.82349198077951</v>
       </c>
       <c r="E5">
-        <v>-11.099</v>
+        <v>-10.632</v>
       </c>
       <c r="F5">
-        <v>1.401</v>
+        <v>1.868</v>
       </c>
       <c r="G5">
         <v>6.07</v>
@@ -1697,28 +1697,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M5">
-        <v>0.0704703</v>
+        <v>0.0939604</v>
       </c>
       <c r="N5">
-        <v>8.379529700000001</v>
+        <v>8.356039600000001</v>
       </c>
       <c r="O5">
-        <v>1.256929455</v>
+        <v>1.25340594</v>
       </c>
       <c r="P5">
-        <v>7.122600245000001</v>
+        <v>7.10263366</v>
       </c>
       <c r="Q5">
-        <v>11.472600245</v>
+        <v>11.45263366</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1037648866862489</v>
+        <v>0.1042804374321399</v>
       </c>
       <c r="T5">
-        <v>0.6944044063721118</v>
+        <v>0.7005805714631077</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>119.9086707449805</v>
+        <v>89.93150305873539</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1018194199348543</v>
+        <v>0.1017042497840472</v>
       </c>
       <c r="C6">
-        <v>46.02549198077951</v>
+        <v>45.58996465002199</v>
       </c>
       <c r="D6">
-        <v>41.82349198077951</v>
+        <v>41.85496465002199</v>
       </c>
       <c r="E6">
-        <v>-10.632</v>
+        <v>-10.165</v>
       </c>
       <c r="F6">
-        <v>1.868</v>
+        <v>2.335</v>
       </c>
       <c r="G6">
         <v>6.07</v>
@@ -1779,28 +1779,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M6">
-        <v>0.0939604</v>
+        <v>0.1174505</v>
       </c>
       <c r="N6">
-        <v>8.356039600000001</v>
+        <v>8.332549500000001</v>
       </c>
       <c r="O6">
-        <v>1.25340594</v>
+        <v>1.249882425</v>
       </c>
       <c r="P6">
-        <v>7.10263366</v>
+        <v>7.082667075000001</v>
       </c>
       <c r="Q6">
-        <v>11.45263366</v>
+        <v>11.432667075</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1042804374321399</v>
+        <v>0.1048068418779444</v>
       </c>
       <c r="T6">
-        <v>0.7005805714631077</v>
+        <v>0.7068867610823351</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>89.93150305873539</v>
+        <v>71.9452024469883</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1017042497840472</v>
+        <v>0.1015890796332401</v>
       </c>
       <c r="C7">
-        <v>45.58996465002199</v>
+        <v>45.15448472204256</v>
       </c>
       <c r="D7">
-        <v>41.85496465002199</v>
+        <v>41.88648472204256</v>
       </c>
       <c r="E7">
-        <v>-10.165</v>
+        <v>-9.698</v>
       </c>
       <c r="F7">
-        <v>2.335</v>
+        <v>2.802</v>
       </c>
       <c r="G7">
         <v>6.07</v>
@@ -1861,28 +1861,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M7">
-        <v>0.1174505</v>
+        <v>0.1409406</v>
       </c>
       <c r="N7">
-        <v>8.332549500000001</v>
+        <v>8.309059400000001</v>
       </c>
       <c r="O7">
-        <v>1.249882425</v>
+        <v>1.24635891</v>
       </c>
       <c r="P7">
-        <v>7.082667075000001</v>
+        <v>7.062700490000001</v>
       </c>
       <c r="Q7">
-        <v>11.432667075</v>
+        <v>11.41270049</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1048068418779444</v>
+        <v>0.1053444464183405</v>
       </c>
       <c r="T7">
-        <v>0.7068867610823351</v>
+        <v>0.71332712494878</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>71.9452024469883</v>
+        <v>59.95433537249025</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1015890796332401</v>
+        <v>0.101473909482433</v>
       </c>
       <c r="C8">
-        <v>45.15448472204258</v>
+        <v>44.71905230401601</v>
       </c>
       <c r="D8">
-        <v>41.88648472204257</v>
+        <v>41.91805230401601</v>
       </c>
       <c r="E8">
-        <v>-9.698</v>
+        <v>-9.231</v>
       </c>
       <c r="F8">
-        <v>2.802</v>
+        <v>3.269</v>
       </c>
       <c r="G8">
         <v>6.07</v>
@@ -1943,28 +1943,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M8">
-        <v>0.1409406</v>
+        <v>0.1644307</v>
       </c>
       <c r="N8">
-        <v>8.309059400000001</v>
+        <v>8.285569300000001</v>
       </c>
       <c r="O8">
-        <v>1.24635891</v>
+        <v>1.242835395</v>
       </c>
       <c r="P8">
-        <v>7.062700490000001</v>
+        <v>7.042733905</v>
       </c>
       <c r="Q8">
-        <v>11.41270049</v>
+        <v>11.392733905</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1053444464183405</v>
+        <v>0.1058936123467021</v>
       </c>
       <c r="T8">
-        <v>0.71332712494878</v>
+        <v>0.7199059912639658</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>59.95433537249026</v>
+        <v>51.38943031927737</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.101473909482433</v>
+        <v>0.1013587393316259</v>
       </c>
       <c r="C9">
-        <v>44.71905230401601</v>
+        <v>44.28366750344039</v>
       </c>
       <c r="D9">
-        <v>41.91805230401601</v>
+        <v>41.94966750344039</v>
       </c>
       <c r="E9">
-        <v>-9.231</v>
+        <v>-8.763999999999999</v>
       </c>
       <c r="F9">
-        <v>3.269000000000001</v>
+        <v>3.736</v>
       </c>
       <c r="G9">
         <v>6.07</v>
@@ -2025,28 +2025,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M9">
-        <v>0.1644307</v>
+        <v>0.1879208</v>
       </c>
       <c r="N9">
-        <v>8.285569300000001</v>
+        <v>8.262079200000001</v>
       </c>
       <c r="O9">
-        <v>1.242835395</v>
+        <v>1.23931188</v>
       </c>
       <c r="P9">
-        <v>7.042733905</v>
+        <v>7.022767320000001</v>
       </c>
       <c r="Q9">
-        <v>11.392733905</v>
+        <v>11.37276732</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1058936123467021</v>
+        <v>0.1064547166648107</v>
       </c>
       <c r="T9">
-        <v>0.7199059912639658</v>
+        <v>0.7266278764120904</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>51.38943031927736</v>
+        <v>44.96575152936769</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1013587393316259</v>
+        <v>0.1012435691808187</v>
       </c>
       <c r="C10">
-        <v>44.28366750344039</v>
+        <v>43.84833042813832</v>
       </c>
       <c r="D10">
-        <v>41.94966750344039</v>
+        <v>41.98133042813832</v>
       </c>
       <c r="E10">
-        <v>-8.763999999999999</v>
+        <v>-8.297000000000001</v>
       </c>
       <c r="F10">
-        <v>3.736</v>
+        <v>4.203</v>
       </c>
       <c r="G10">
         <v>6.07</v>
@@ -2107,28 +2107,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M10">
-        <v>0.1879208</v>
+        <v>0.2114109</v>
       </c>
       <c r="N10">
-        <v>8.262079200000001</v>
+        <v>8.2385891</v>
       </c>
       <c r="O10">
-        <v>1.23931188</v>
+        <v>1.235788365</v>
       </c>
       <c r="P10">
-        <v>7.022767320000001</v>
+        <v>7.002800735</v>
       </c>
       <c r="Q10">
-        <v>11.37276732</v>
+        <v>11.352800735</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1064547166648107</v>
+        <v>0.1070281529459546</v>
       </c>
       <c r="T10">
-        <v>0.7266278764120904</v>
+        <v>0.7334974952997341</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>44.96575152936769</v>
+        <v>39.9695569149935</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1012435691808187</v>
+        <v>0.1011283990300116</v>
       </c>
       <c r="C11">
-        <v>43.84833042813832</v>
+        <v>43.41304118625823</v>
       </c>
       <c r="D11">
-        <v>41.98133042813832</v>
+        <v>42.01304118625823</v>
       </c>
       <c r="E11">
-        <v>-8.297000000000001</v>
+        <v>-7.83</v>
       </c>
       <c r="F11">
-        <v>4.203</v>
+        <v>4.67</v>
       </c>
       <c r="G11">
         <v>6.07</v>
@@ -2189,28 +2189,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M11">
-        <v>0.2114109</v>
+        <v>0.234901</v>
       </c>
       <c r="N11">
-        <v>8.2385891</v>
+        <v>8.215099</v>
       </c>
       <c r="O11">
-        <v>1.235788365</v>
+        <v>1.23226485</v>
       </c>
       <c r="P11">
-        <v>7.002800735</v>
+        <v>6.98283415</v>
       </c>
       <c r="Q11">
-        <v>11.352800735</v>
+        <v>11.33283415</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1070281529459546</v>
+        <v>0.1076143322555684</v>
       </c>
       <c r="T11">
-        <v>0.7334974952997341</v>
+        <v>0.7405197723848812</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>39.9695569149935</v>
+        <v>35.97260122349416</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1011283990300116</v>
+        <v>0.1010132288792045</v>
       </c>
       <c r="C12">
-        <v>43.41304118625823</v>
+        <v>42.97779988627551</v>
       </c>
       <c r="D12">
-        <v>42.01304118625823</v>
+        <v>42.04479988627551</v>
       </c>
       <c r="E12">
-        <v>-7.829999999999999</v>
+        <v>-7.363</v>
       </c>
       <c r="F12">
-        <v>4.670000000000001</v>
+        <v>5.137</v>
       </c>
       <c r="G12">
         <v>6.07</v>
@@ -2271,28 +2271,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M12">
-        <v>0.234901</v>
+        <v>0.2583911</v>
       </c>
       <c r="N12">
-        <v>8.215099</v>
+        <v>8.1916089</v>
       </c>
       <c r="O12">
-        <v>1.23226485</v>
+        <v>1.228741335</v>
       </c>
       <c r="P12">
-        <v>6.98283415</v>
+        <v>6.962867565</v>
       </c>
       <c r="Q12">
-        <v>11.33283415</v>
+        <v>11.312867565</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1076143322555684</v>
+        <v>0.1082136841339376</v>
       </c>
       <c r="T12">
-        <v>0.7405197723848812</v>
+        <v>0.7476998534494697</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>35.97260122349415</v>
+        <v>32.70236474863106</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1010132288792045</v>
+        <v>0.1008980587283973</v>
       </c>
       <c r="C13">
-        <v>42.97779988627551</v>
+        <v>42.54260663699382</v>
       </c>
       <c r="D13">
-        <v>42.04479988627551</v>
+        <v>42.07660663699382</v>
       </c>
       <c r="E13">
-        <v>-7.363</v>
+        <v>-6.896</v>
       </c>
       <c r="F13">
-        <v>5.137</v>
+        <v>5.604</v>
       </c>
       <c r="G13">
         <v>6.07</v>
@@ -2353,28 +2353,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M13">
-        <v>0.2583911</v>
+        <v>0.2818812</v>
       </c>
       <c r="N13">
-        <v>8.1916089</v>
+        <v>8.1681188</v>
       </c>
       <c r="O13">
-        <v>1.228741335</v>
+        <v>1.22521782</v>
       </c>
       <c r="P13">
-        <v>6.962867565</v>
+        <v>6.94290098</v>
       </c>
       <c r="Q13">
-        <v>11.312867565</v>
+        <v>11.29290098</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1082136841339376</v>
+        <v>0.1088266576459061</v>
       </c>
       <c r="T13">
-        <v>0.7476998534494697</v>
+        <v>0.7550431181746169</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.70236474863106</v>
+        <v>29.97716768624513</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1008980587283973</v>
+        <v>0.1007828885775902</v>
       </c>
       <c r="C14">
-        <v>42.54260663699382</v>
+        <v>42.1074615475463</v>
       </c>
       <c r="D14">
-        <v>42.07660663699382</v>
+        <v>42.1084615475463</v>
       </c>
       <c r="E14">
-        <v>-6.896</v>
+        <v>-6.428999999999999</v>
       </c>
       <c r="F14">
-        <v>5.604</v>
+        <v>6.071000000000001</v>
       </c>
       <c r="G14">
         <v>6.07</v>
@@ -2435,28 +2435,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M14">
-        <v>0.2818812</v>
+        <v>0.3053713</v>
       </c>
       <c r="N14">
-        <v>8.1681188</v>
+        <v>8.144628700000002</v>
       </c>
       <c r="O14">
-        <v>1.22521782</v>
+        <v>1.221694305</v>
       </c>
       <c r="P14">
-        <v>6.94290098</v>
+        <v>6.922934395000002</v>
       </c>
       <c r="Q14">
-        <v>11.29290098</v>
+        <v>11.272934395</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1088266576459061</v>
+        <v>0.1094537225029772</v>
       </c>
       <c r="T14">
-        <v>0.7550431181746169</v>
+        <v>0.7625551935831009</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.97716768624513</v>
+        <v>27.67123171038012</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1007828885775902</v>
+        <v>0.1006677184267831</v>
       </c>
       <c r="C15">
-        <v>42.1074615475463</v>
+        <v>41.67236472739683</v>
       </c>
       <c r="D15">
-        <v>42.1084615475463</v>
+        <v>42.14036472739683</v>
       </c>
       <c r="E15">
-        <v>-6.428999999999999</v>
+        <v>-5.961999999999999</v>
       </c>
       <c r="F15">
-        <v>6.071000000000001</v>
+        <v>6.538000000000001</v>
       </c>
       <c r="G15">
         <v>6.07</v>
@@ -2517,28 +2517,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M15">
-        <v>0.3053713</v>
+        <v>0.3288614</v>
       </c>
       <c r="N15">
-        <v>8.144628700000002</v>
+        <v>8.121138600000002</v>
       </c>
       <c r="O15">
-        <v>1.221694305</v>
+        <v>1.21817079</v>
       </c>
       <c r="P15">
-        <v>6.922934395000002</v>
+        <v>6.902967810000002</v>
       </c>
       <c r="Q15">
-        <v>11.272934395</v>
+        <v>11.25296781</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1094537225029772</v>
+        <v>0.1100953702637013</v>
       </c>
       <c r="T15">
-        <v>0.7625551935831009</v>
+        <v>0.7702419684196892</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.67123171038012</v>
+        <v>25.69471515963868</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1006677184267831</v>
+        <v>0.100552548275976</v>
       </c>
       <c r="C16">
-        <v>41.67236472739683</v>
+        <v>41.23731628634128</v>
       </c>
       <c r="D16">
-        <v>42.14036472739683</v>
+        <v>42.17231628634128</v>
       </c>
       <c r="E16">
-        <v>-5.961999999999999</v>
+        <v>-5.494999999999998</v>
       </c>
       <c r="F16">
-        <v>6.538000000000001</v>
+        <v>7.005000000000002</v>
       </c>
       <c r="G16">
         <v>6.07</v>
@@ -2599,28 +2599,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M16">
-        <v>0.3288614</v>
+        <v>0.3523515</v>
       </c>
       <c r="N16">
-        <v>8.121138600000002</v>
+        <v>8.097648500000002</v>
       </c>
       <c r="O16">
-        <v>1.21817079</v>
+        <v>1.214647275</v>
       </c>
       <c r="P16">
-        <v>6.902967810000002</v>
+        <v>6.883001225000002</v>
       </c>
       <c r="Q16">
-        <v>11.25296781</v>
+        <v>11.233001225</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1100953702637013</v>
+        <v>0.1107521156187952</v>
       </c>
       <c r="T16">
-        <v>0.7702419684196892</v>
+        <v>0.7781096085465501</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.69471515963868</v>
+        <v>23.9817341489961</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.100552548275976</v>
+        <v>0.1004373781251688</v>
       </c>
       <c r="C17">
-        <v>41.23731628634128</v>
+        <v>40.80231633450877</v>
       </c>
       <c r="D17">
-        <v>42.17231628634128</v>
+        <v>42.20431633450877</v>
       </c>
       <c r="E17">
-        <v>-5.495</v>
+        <v>-5.028</v>
       </c>
       <c r="F17">
-        <v>7.005</v>
+        <v>7.472</v>
       </c>
       <c r="G17">
         <v>6.07</v>
@@ -2681,28 +2681,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M17">
-        <v>0.3523515</v>
+        <v>0.3758416</v>
       </c>
       <c r="N17">
-        <v>8.097648500000002</v>
+        <v>8.074158400000002</v>
       </c>
       <c r="O17">
-        <v>1.214647275</v>
+        <v>1.21112376</v>
       </c>
       <c r="P17">
-        <v>6.883001225000002</v>
+        <v>6.863034640000001</v>
       </c>
       <c r="Q17">
-        <v>11.233001225</v>
+        <v>11.21303464</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1107521156187952</v>
+        <v>0.1114244977680582</v>
       </c>
       <c r="T17">
-        <v>0.7781096085465501</v>
+        <v>0.7861645734383365</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.98173414899611</v>
+        <v>22.48287576468385</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1004373781251688</v>
+        <v>0.1003222079743617</v>
       </c>
       <c r="C18">
-        <v>40.80231633450877</v>
+        <v>40.36736498236294</v>
       </c>
       <c r="D18">
-        <v>42.20431633450877</v>
+        <v>42.23636498236294</v>
       </c>
       <c r="E18">
-        <v>-5.028</v>
+        <v>-4.560999999999999</v>
       </c>
       <c r="F18">
-        <v>7.472</v>
+        <v>7.939000000000001</v>
       </c>
       <c r="G18">
         <v>6.07</v>
@@ -2763,28 +2763,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M18">
-        <v>0.3758416</v>
+        <v>0.3993317</v>
       </c>
       <c r="N18">
-        <v>8.074158400000002</v>
+        <v>8.050668300000002</v>
       </c>
       <c r="O18">
-        <v>1.21112376</v>
+        <v>1.207600245</v>
       </c>
       <c r="P18">
-        <v>6.863034640000001</v>
+        <v>6.843068055000002</v>
       </c>
       <c r="Q18">
-        <v>11.21303464</v>
+        <v>11.193068055</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1114244977680582</v>
+        <v>0.1121130818968213</v>
       </c>
       <c r="T18">
-        <v>0.7861645734383365</v>
+        <v>0.7944136338696838</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.48287576468385</v>
+        <v>21.16035366087892</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1003222079743617</v>
+        <v>0.1002070378235546</v>
       </c>
       <c r="C19">
-        <v>40.36736498236294</v>
+        <v>39.9324623407032</v>
       </c>
       <c r="D19">
-        <v>42.23636498236294</v>
+        <v>42.26846234070319</v>
       </c>
       <c r="E19">
-        <v>-4.560999999999999</v>
+        <v>-4.093999999999998</v>
       </c>
       <c r="F19">
-        <v>7.939000000000001</v>
+        <v>8.406000000000002</v>
       </c>
       <c r="G19">
         <v>6.07</v>
@@ -2845,28 +2845,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M19">
-        <v>0.3993317</v>
+        <v>0.4228218000000001</v>
       </c>
       <c r="N19">
-        <v>8.050668300000002</v>
+        <v>8.027178200000002</v>
       </c>
       <c r="O19">
-        <v>1.207600245</v>
+        <v>1.20407673</v>
       </c>
       <c r="P19">
-        <v>6.843068055000002</v>
+        <v>6.823101470000001</v>
       </c>
       <c r="Q19">
-        <v>11.193068055</v>
+        <v>11.17310147</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1121130818968213</v>
+        <v>0.1128184607604324</v>
       </c>
       <c r="T19">
-        <v>0.7944136338696838</v>
+        <v>0.8028638908969176</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.16035366087892</v>
+        <v>19.98477845749675</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1002070378235546</v>
+        <v>0.1000918676727475</v>
       </c>
       <c r="C20">
-        <v>39.9324623407032</v>
+        <v>39.49760852066601</v>
       </c>
       <c r="D20">
-        <v>42.26846234070319</v>
+        <v>42.30060852066601</v>
       </c>
       <c r="E20">
-        <v>-4.093999999999999</v>
+        <v>-3.626999999999999</v>
       </c>
       <c r="F20">
-        <v>8.406000000000001</v>
+        <v>8.873000000000001</v>
       </c>
       <c r="G20">
         <v>6.07</v>
@@ -2927,28 +2927,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M20">
-        <v>0.4228218</v>
+        <v>0.4463119</v>
       </c>
       <c r="N20">
-        <v>8.027178200000002</v>
+        <v>8.003688100000002</v>
       </c>
       <c r="O20">
-        <v>1.20407673</v>
+        <v>1.200553215</v>
       </c>
       <c r="P20">
-        <v>6.823101470000001</v>
+        <v>6.803134885000001</v>
       </c>
       <c r="Q20">
-        <v>11.17310147</v>
+        <v>11.153134885</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1128184607604324</v>
+        <v>0.113541256386108</v>
       </c>
       <c r="T20">
-        <v>0.8028638908969176</v>
+        <v>0.8115227962458116</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.98477845749676</v>
+        <v>18.93294801236534</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1000918676727475</v>
+        <v>0.09997669752194036</v>
       </c>
       <c r="C21">
-        <v>39.49760852066601</v>
+        <v>39.06280363372623</v>
       </c>
       <c r="D21">
-        <v>42.30060852066601</v>
+        <v>42.33280363372624</v>
       </c>
       <c r="E21">
-        <v>-3.626999999999999</v>
+        <v>-3.159999999999998</v>
       </c>
       <c r="F21">
-        <v>8.873000000000001</v>
+        <v>9.340000000000002</v>
       </c>
       <c r="G21">
         <v>6.07</v>
@@ -3009,28 +3009,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M21">
-        <v>0.4463119</v>
+        <v>0.4698020000000001</v>
       </c>
       <c r="N21">
-        <v>8.003688100000002</v>
+        <v>7.980198000000001</v>
       </c>
       <c r="O21">
-        <v>1.200553215</v>
+        <v>1.1970297</v>
       </c>
       <c r="P21">
-        <v>6.803134885000001</v>
+        <v>6.783168300000002</v>
       </c>
       <c r="Q21">
-        <v>11.153134885</v>
+        <v>11.1331683</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.113541256386108</v>
+        <v>0.1142821219024254</v>
       </c>
       <c r="T21">
-        <v>0.8115227962458116</v>
+        <v>0.8203981742284279</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.93294801236534</v>
+        <v>17.98630061174708</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09997669752194036</v>
+        <v>0.09986152737113324</v>
       </c>
       <c r="C22">
-        <v>39.06280363372623</v>
+        <v>38.62804779169831</v>
       </c>
       <c r="D22">
-        <v>42.33280363372624</v>
+        <v>42.36504779169831</v>
       </c>
       <c r="E22">
-        <v>-3.159999999999998</v>
+        <v>-2.692999999999998</v>
       </c>
       <c r="F22">
-        <v>9.340000000000002</v>
+        <v>9.807000000000002</v>
       </c>
       <c r="G22">
         <v>6.07</v>
@@ -3091,28 +3091,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M22">
-        <v>0.4698020000000001</v>
+        <v>0.4932921000000001</v>
       </c>
       <c r="N22">
-        <v>7.980198000000001</v>
+        <v>7.956707900000001</v>
       </c>
       <c r="O22">
-        <v>1.1970297</v>
+        <v>1.193506185</v>
       </c>
       <c r="P22">
-        <v>6.783168300000002</v>
+        <v>6.763201715000001</v>
       </c>
       <c r="Q22">
-        <v>11.1331683</v>
+        <v>11.113201715</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1142821219024254</v>
+        <v>0.1150417435077636</v>
       </c>
       <c r="T22">
-        <v>0.8203981742284279</v>
+        <v>0.8294982453245282</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.98630061174708</v>
+        <v>17.12981010642579</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09986152737113321</v>
+        <v>0.09974635722032611</v>
       </c>
       <c r="C23">
-        <v>38.62804779169832</v>
+        <v>38.19334110673763</v>
       </c>
       <c r="D23">
-        <v>42.36504779169832</v>
+        <v>42.39734110673763</v>
       </c>
       <c r="E23">
-        <v>-2.693</v>
+        <v>-2.225999999999999</v>
       </c>
       <c r="F23">
-        <v>9.807</v>
+        <v>10.274</v>
       </c>
       <c r="G23">
         <v>6.07</v>
@@ -3173,28 +3173,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M23">
-        <v>0.4932921</v>
+        <v>0.5167822</v>
       </c>
       <c r="N23">
-        <v>7.956707900000001</v>
+        <v>7.933217800000001</v>
       </c>
       <c r="O23">
-        <v>1.193506185</v>
+        <v>1.18998267</v>
       </c>
       <c r="P23">
-        <v>6.763201715000001</v>
+        <v>6.743235130000001</v>
       </c>
       <c r="Q23">
-        <v>11.113201715</v>
+        <v>11.09323513</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1150417435077636</v>
+        <v>0.1158208425901617</v>
       </c>
       <c r="T23">
-        <v>0.8294982453245281</v>
+        <v>0.8388316515769387</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.12981010642579</v>
+        <v>16.35118237431553</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09974635722032611</v>
+        <v>0.09963118706951897</v>
       </c>
       <c r="C24">
-        <v>38.19334110673763</v>
+        <v>37.75868369134183</v>
       </c>
       <c r="D24">
-        <v>42.39734110673763</v>
+        <v>42.42968369134183</v>
       </c>
       <c r="E24">
-        <v>-2.225999999999999</v>
+        <v>-1.758999999999999</v>
       </c>
       <c r="F24">
-        <v>10.274</v>
+        <v>10.741</v>
       </c>
       <c r="G24">
         <v>6.07</v>
@@ -3255,28 +3255,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M24">
-        <v>0.5167822</v>
+        <v>0.5402723</v>
       </c>
       <c r="N24">
-        <v>7.933217800000001</v>
+        <v>7.909727700000001</v>
       </c>
       <c r="O24">
-        <v>1.18998267</v>
+        <v>1.186459155</v>
       </c>
       <c r="P24">
-        <v>6.743235130000001</v>
+        <v>6.723268545000002</v>
       </c>
       <c r="Q24">
-        <v>11.09323513</v>
+        <v>11.073268545</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1158208425901617</v>
+        <v>0.1166201780123623</v>
       </c>
       <c r="T24">
-        <v>0.8388316515769387</v>
+        <v>0.8484074839657755</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.35118237431553</v>
+        <v>15.6402614015192</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09963118706951897</v>
+        <v>0.09951601691871186</v>
       </c>
       <c r="C25">
-        <v>37.75868369134183</v>
+        <v>37.32407565835203</v>
       </c>
       <c r="D25">
-        <v>42.42968369134183</v>
+        <v>42.46207565835203</v>
       </c>
       <c r="E25">
-        <v>-1.758999999999999</v>
+        <v>-1.291999999999998</v>
       </c>
       <c r="F25">
-        <v>10.741</v>
+        <v>11.208</v>
       </c>
       <c r="G25">
         <v>6.07</v>
@@ -3337,28 +3337,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M25">
-        <v>0.5402723</v>
+        <v>0.5637624000000001</v>
       </c>
       <c r="N25">
-        <v>7.909727700000001</v>
+        <v>7.886237600000001</v>
       </c>
       <c r="O25">
-        <v>1.186459155</v>
+        <v>1.18293564</v>
       </c>
       <c r="P25">
-        <v>6.723268545000002</v>
+        <v>6.703301960000001</v>
       </c>
       <c r="Q25">
-        <v>11.073268545</v>
+        <v>11.05330196</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1166201780123623</v>
+        <v>0.1174405485772524</v>
       </c>
       <c r="T25">
-        <v>0.8484074839657755</v>
+        <v>0.8582353119437922</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.6402614015192</v>
+        <v>14.98858384312256</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09951601691871186</v>
+        <v>0.09940084676790471</v>
       </c>
       <c r="C26">
-        <v>37.32407565835203</v>
+        <v>36.88951712095425</v>
       </c>
       <c r="D26">
-        <v>42.46207565835203</v>
+        <v>42.49451712095425</v>
       </c>
       <c r="E26">
-        <v>-1.292</v>
+        <v>-0.8249999999999993</v>
       </c>
       <c r="F26">
-        <v>11.208</v>
+        <v>11.675</v>
       </c>
       <c r="G26">
         <v>6.07</v>
@@ -3419,28 +3419,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M26">
-        <v>0.5637624</v>
+        <v>0.5872525</v>
       </c>
       <c r="N26">
-        <v>7.886237600000001</v>
+        <v>7.862747500000001</v>
       </c>
       <c r="O26">
-        <v>1.18293564</v>
+        <v>1.179412125</v>
       </c>
       <c r="P26">
-        <v>6.703301960000001</v>
+        <v>6.683335375000001</v>
       </c>
       <c r="Q26">
-        <v>11.05330196</v>
+        <v>11.033335375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1174405485772524</v>
+        <v>0.1182827956905396</v>
       </c>
       <c r="T26">
-        <v>0.8582353119437922</v>
+        <v>0.868325215334556</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.98858384312257</v>
+        <v>14.38904048939766</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09940084676790471</v>
+        <v>0.0992856766170976</v>
       </c>
       <c r="C27">
-        <v>36.88951712095425</v>
+        <v>36.45500819268063</v>
       </c>
       <c r="D27">
-        <v>42.49451712095425</v>
+        <v>42.52700819268063</v>
       </c>
       <c r="E27">
-        <v>-0.8249999999999993</v>
+        <v>-0.3579999999999988</v>
       </c>
       <c r="F27">
-        <v>11.675</v>
+        <v>12.142</v>
       </c>
       <c r="G27">
         <v>6.07</v>
@@ -3501,28 +3501,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M27">
-        <v>0.5872525</v>
+        <v>0.6107426</v>
       </c>
       <c r="N27">
-        <v>7.862747500000001</v>
+        <v>7.839257400000001</v>
       </c>
       <c r="O27">
-        <v>1.179412125</v>
+        <v>1.17588861</v>
       </c>
       <c r="P27">
-        <v>6.683335375000001</v>
+        <v>6.663368790000001</v>
       </c>
       <c r="Q27">
-        <v>11.033335375</v>
+        <v>11.01336879</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1182827956905396</v>
+        <v>0.1191478062393211</v>
       </c>
       <c r="T27">
-        <v>0.868325215334556</v>
+        <v>0.878687818816962</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.38904048939766</v>
+        <v>13.83561585519006</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0992856766170976</v>
+        <v>0.09917050646629048</v>
       </c>
       <c r="C28">
-        <v>36.45500819268063</v>
+        <v>36.02054898741085</v>
       </c>
       <c r="D28">
-        <v>42.52700819268063</v>
+        <v>42.55954898741085</v>
       </c>
       <c r="E28">
-        <v>-0.3579999999999988</v>
+        <v>0.1090000000000018</v>
       </c>
       <c r="F28">
-        <v>12.142</v>
+        <v>12.609</v>
       </c>
       <c r="G28">
         <v>6.07</v>
@@ -3583,28 +3583,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M28">
-        <v>0.6107426</v>
+        <v>0.6342327000000001</v>
       </c>
       <c r="N28">
-        <v>7.839257400000001</v>
+        <v>7.815767300000001</v>
       </c>
       <c r="O28">
-        <v>1.17588861</v>
+        <v>1.172365095</v>
       </c>
       <c r="P28">
-        <v>6.663368790000001</v>
+        <v>6.643402205000001</v>
       </c>
       <c r="Q28">
-        <v>11.01336879</v>
+        <v>10.993402205</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1191478062393211</v>
+        <v>0.1200365157072472</v>
       </c>
       <c r="T28">
-        <v>0.878687818816962</v>
+        <v>0.8893343292440917</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.83561585519006</v>
+        <v>13.32318563833117</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09917050646629048</v>
+        <v>0.09941233631548337</v>
       </c>
       <c r="C29">
-        <v>36.02054898741085</v>
+        <v>35.48527848601483</v>
       </c>
       <c r="D29">
-        <v>42.55954898741085</v>
+        <v>42.49127848601483</v>
       </c>
       <c r="E29">
-        <v>0.1090000000000018</v>
+        <v>0.5760000000000023</v>
       </c>
       <c r="F29">
-        <v>12.609</v>
+        <v>13.076</v>
       </c>
       <c r="G29">
         <v>6.07</v>
@@ -3665,45 +3665,45 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M29">
-        <v>0.6342327000000001</v>
+        <v>0.6773368000000001</v>
       </c>
       <c r="N29">
-        <v>7.815767300000001</v>
+        <v>7.772663200000001</v>
       </c>
       <c r="O29">
-        <v>1.172365095</v>
+        <v>1.16589948</v>
       </c>
       <c r="P29">
-        <v>6.643402205000001</v>
+        <v>6.606763720000001</v>
       </c>
       <c r="Q29">
-        <v>10.993402205</v>
+        <v>10.95676372</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1200365157072472</v>
+        <v>0.1209499115492824</v>
       </c>
       <c r="T29">
-        <v>0.8893343292440917</v>
+        <v>0.9002765760719749</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.15</v>
       </c>
       <c r="W29">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>13.32318563833117</v>
+        <v>12.47532985067399</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09941233631548337</v>
+        <v>0.09930991616467624</v>
       </c>
       <c r="C30">
-        <v>35.48527848601483</v>
+        <v>35.04716575798274</v>
       </c>
       <c r="D30">
-        <v>42.49127848601483</v>
+        <v>42.52016575798275</v>
       </c>
       <c r="E30">
-        <v>0.5760000000000023</v>
+        <v>1.043000000000003</v>
       </c>
       <c r="F30">
-        <v>13.076</v>
+        <v>13.543</v>
       </c>
       <c r="G30">
         <v>6.07</v>
@@ -3747,28 +3747,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M30">
-        <v>0.6773368000000001</v>
+        <v>0.7015274000000001</v>
       </c>
       <c r="N30">
-        <v>7.772663200000001</v>
+        <v>7.748472600000001</v>
       </c>
       <c r="O30">
-        <v>1.16589948</v>
+        <v>1.16227089</v>
       </c>
       <c r="P30">
-        <v>6.606763720000001</v>
+        <v>6.586201710000001</v>
       </c>
       <c r="Q30">
-        <v>10.95676372</v>
+        <v>10.93620171</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1209499115492824</v>
+        <v>0.1218890368516567</v>
       </c>
       <c r="T30">
-        <v>0.9002765760719749</v>
+        <v>0.9115270552048688</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.47532985067399</v>
+        <v>12.04514606271972</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09930991616467623</v>
+        <v>0.09920749601386909</v>
       </c>
       <c r="C31">
-        <v>35.04716575798275</v>
+        <v>34.60909233411879</v>
       </c>
       <c r="D31">
-        <v>42.52016575798275</v>
+        <v>42.54909233411879</v>
       </c>
       <c r="E31">
-        <v>1.042999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="F31">
-        <v>13.543</v>
+        <v>14.01</v>
       </c>
       <c r="G31">
         <v>6.07</v>
@@ -3829,28 +3829,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M31">
-        <v>0.7015273999999999</v>
+        <v>0.725718</v>
       </c>
       <c r="N31">
-        <v>7.748472600000001</v>
+        <v>7.724282000000001</v>
       </c>
       <c r="O31">
-        <v>1.16227089</v>
+        <v>1.1586423</v>
       </c>
       <c r="P31">
-        <v>6.586201710000001</v>
+        <v>6.565639700000001</v>
       </c>
       <c r="Q31">
-        <v>10.93620171</v>
+        <v>10.9156397</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1218890368516567</v>
+        <v>0.1228549943055273</v>
       </c>
       <c r="T31">
-        <v>0.9115270552048688</v>
+        <v>0.9230989765987024</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.04514606271972</v>
+        <v>11.6436411939624</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09920749601386909</v>
+        <v>0.09910507586306197</v>
       </c>
       <c r="C32">
-        <v>34.60909233411879</v>
+        <v>34.17105829469375</v>
       </c>
       <c r="D32">
-        <v>42.54909233411879</v>
+        <v>42.57805829469375</v>
       </c>
       <c r="E32">
-        <v>1.51</v>
+        <v>1.977</v>
       </c>
       <c r="F32">
-        <v>14.01</v>
+        <v>14.477</v>
       </c>
       <c r="G32">
         <v>6.07</v>
@@ -3911,28 +3911,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M32">
-        <v>0.725718</v>
+        <v>0.7499086</v>
       </c>
       <c r="N32">
-        <v>7.724282000000001</v>
+        <v>7.700091400000001</v>
       </c>
       <c r="O32">
-        <v>1.1586423</v>
+        <v>1.15501371</v>
       </c>
       <c r="P32">
-        <v>6.565639700000001</v>
+        <v>6.545077690000001</v>
       </c>
       <c r="Q32">
-        <v>10.9156397</v>
+        <v>10.89507769</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1228549943055273</v>
+        <v>0.1238489505261768</v>
       </c>
       <c r="T32">
-        <v>0.9230989765987024</v>
+        <v>0.9350063160039517</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.6436411939624</v>
+        <v>11.2680398651249</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09910507586306197</v>
+        <v>0.09900265571225483</v>
       </c>
       <c r="C33">
-        <v>34.17105829469375</v>
+        <v>33.73306372019713</v>
       </c>
       <c r="D33">
-        <v>42.57805829469375</v>
+        <v>42.60706372019713</v>
       </c>
       <c r="E33">
-        <v>1.977</v>
+        <v>2.444000000000001</v>
       </c>
       <c r="F33">
-        <v>14.477</v>
+        <v>14.944</v>
       </c>
       <c r="G33">
         <v>6.07</v>
@@ -3993,28 +3993,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M33">
-        <v>0.7499086</v>
+        <v>0.7740992</v>
       </c>
       <c r="N33">
-        <v>7.700091400000001</v>
+        <v>7.675900800000001</v>
       </c>
       <c r="O33">
-        <v>1.15501371</v>
+        <v>1.15138512</v>
       </c>
       <c r="P33">
-        <v>6.545077690000001</v>
+        <v>6.52451568</v>
       </c>
       <c r="Q33">
-        <v>10.89507769</v>
+        <v>10.87451568</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1238489505261768</v>
+        <v>0.124872140753316</v>
       </c>
       <c r="T33">
-        <v>0.9350063160039517</v>
+        <v>0.9472638712740611</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.2680398651249</v>
+        <v>10.91591361933975</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09900265571225483</v>
+        <v>0.09890023556144772</v>
       </c>
       <c r="C34">
-        <v>33.73306372019713</v>
+        <v>33.29510869133792</v>
       </c>
       <c r="D34">
-        <v>42.60706372019713</v>
+        <v>42.63610869133792</v>
       </c>
       <c r="E34">
-        <v>2.444000000000001</v>
+        <v>2.911000000000001</v>
       </c>
       <c r="F34">
-        <v>14.944</v>
+        <v>15.411</v>
       </c>
       <c r="G34">
         <v>6.07</v>
@@ -4075,28 +4075,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M34">
-        <v>0.7740992</v>
+        <v>0.7982898</v>
       </c>
       <c r="N34">
-        <v>7.675900800000001</v>
+        <v>7.651710200000001</v>
       </c>
       <c r="O34">
-        <v>1.15138512</v>
+        <v>1.14775653</v>
       </c>
       <c r="P34">
-        <v>6.52451568</v>
+        <v>6.503953670000001</v>
       </c>
       <c r="Q34">
-        <v>10.87451568</v>
+        <v>10.85395367</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.124872140753316</v>
+        <v>0.1259258739723101</v>
       </c>
       <c r="T34">
-        <v>0.9472638712740611</v>
+        <v>0.9598873237164127</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.91591361933975</v>
+        <v>10.58512835814763</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09890023556144772</v>
+        <v>0.09879781541064062</v>
       </c>
       <c r="C35">
-        <v>33.29510869133792</v>
+        <v>32.85719328904536</v>
       </c>
       <c r="D35">
-        <v>42.63610869133792</v>
+        <v>42.66519328904536</v>
       </c>
       <c r="E35">
-        <v>2.911000000000001</v>
+        <v>3.378000000000002</v>
       </c>
       <c r="F35">
-        <v>15.411</v>
+        <v>15.878</v>
       </c>
       <c r="G35">
         <v>6.07</v>
@@ -4157,28 +4157,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M35">
-        <v>0.7982898</v>
+        <v>0.8224804000000001</v>
       </c>
       <c r="N35">
-        <v>7.651710200000001</v>
+        <v>7.627519600000001</v>
       </c>
       <c r="O35">
-        <v>1.14775653</v>
+        <v>1.14412794</v>
       </c>
       <c r="P35">
-        <v>6.503953670000001</v>
+        <v>6.483391660000001</v>
       </c>
       <c r="Q35">
-        <v>10.85395367</v>
+        <v>10.83339166</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1259258739723101</v>
+        <v>0.1270115385009706</v>
       </c>
       <c r="T35">
-        <v>0.9598873237164127</v>
+        <v>0.9728933050206537</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.58512835814763</v>
+        <v>10.27380105349623</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09879781541064062</v>
+        <v>0.09869539525983348</v>
       </c>
       <c r="C36">
-        <v>32.85719328904536</v>
+        <v>32.41931759446963</v>
       </c>
       <c r="D36">
-        <v>42.66519328904536</v>
+        <v>42.69431759446963</v>
       </c>
       <c r="E36">
-        <v>3.378000000000002</v>
+        <v>3.845000000000002</v>
       </c>
       <c r="F36">
-        <v>15.878</v>
+        <v>16.345</v>
       </c>
       <c r="G36">
         <v>6.07</v>
@@ -4239,28 +4239,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M36">
-        <v>0.8224804000000001</v>
+        <v>0.8466710000000001</v>
       </c>
       <c r="N36">
-        <v>7.627519600000001</v>
+        <v>7.603329000000001</v>
       </c>
       <c r="O36">
-        <v>1.14412794</v>
+        <v>1.14049935</v>
       </c>
       <c r="P36">
-        <v>6.483391660000001</v>
+        <v>6.462829650000002</v>
       </c>
       <c r="Q36">
-        <v>10.83339166</v>
+        <v>10.81282965</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1270115385009706</v>
+        <v>0.1281306080920515</v>
       </c>
       <c r="T36">
-        <v>0.9728933050206537</v>
+        <v>0.9862994703650253</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.27380105349623</v>
+        <v>9.980263880539194</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09869539525983348</v>
+        <v>0.09911317510902634</v>
       </c>
       <c r="C37">
-        <v>32.41931759446963</v>
+        <v>31.83376627003636</v>
       </c>
       <c r="D37">
-        <v>42.69431759446963</v>
+        <v>42.57576627003636</v>
       </c>
       <c r="E37">
-        <v>3.845000000000002</v>
+        <v>4.312000000000005</v>
       </c>
       <c r="F37">
-        <v>16.345</v>
+        <v>16.812</v>
       </c>
       <c r="G37">
         <v>6.07</v>
@@ -4321,45 +4321,45 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M37">
-        <v>0.8466710000000001</v>
+        <v>0.8994420000000002</v>
       </c>
       <c r="N37">
-        <v>7.603329000000001</v>
+        <v>7.550558000000001</v>
       </c>
       <c r="O37">
-        <v>1.14049935</v>
+        <v>1.1325837</v>
       </c>
       <c r="P37">
-        <v>6.462829650000002</v>
+        <v>6.417974300000001</v>
       </c>
       <c r="Q37">
-        <v>10.81282965</v>
+        <v>10.7679743</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1281306080920515</v>
+        <v>0.1292846486078537</v>
       </c>
       <c r="T37">
-        <v>0.9862994703650253</v>
+        <v>1.000124578376408</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.15</v>
       </c>
       <c r="W37">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>9.980263880539194</v>
+        <v>9.39471361132791</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09911317510902636</v>
+        <v>0.09902520495821925</v>
       </c>
       <c r="C38">
-        <v>31.83376627003635</v>
+        <v>31.39167437318738</v>
       </c>
       <c r="D38">
-        <v>42.57576627003635</v>
+        <v>42.60067437318738</v>
       </c>
       <c r="E38">
-        <v>4.312000000000001</v>
+        <v>4.779</v>
       </c>
       <c r="F38">
-        <v>16.812</v>
+        <v>17.279</v>
       </c>
       <c r="G38">
         <v>6.07</v>
@@ -4403,28 +4403,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M38">
-        <v>0.8994420000000001</v>
+        <v>0.9244264999999999</v>
       </c>
       <c r="N38">
-        <v>7.550558000000001</v>
+        <v>7.525573500000001</v>
       </c>
       <c r="O38">
-        <v>1.1325837</v>
+        <v>1.128836025</v>
       </c>
       <c r="P38">
-        <v>6.417974300000001</v>
+        <v>6.396737475000001</v>
       </c>
       <c r="Q38">
-        <v>10.7679743</v>
+        <v>10.746737475</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1292846486078537</v>
+        <v>0.1304753253305067</v>
       </c>
       <c r="T38">
-        <v>1.000124578376408</v>
+        <v>1.014388578705613</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.394713611327912</v>
+        <v>9.140802432643376</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09902520495821925</v>
+        <v>0.09893723480741212</v>
       </c>
       <c r="C39">
-        <v>31.39167437318738</v>
+        <v>30.94961163737671</v>
       </c>
       <c r="D39">
-        <v>42.60067437318738</v>
+        <v>42.62561163737671</v>
       </c>
       <c r="E39">
-        <v>4.779</v>
+        <v>5.246000000000002</v>
       </c>
       <c r="F39">
-        <v>17.279</v>
+        <v>17.746</v>
       </c>
       <c r="G39">
         <v>6.07</v>
@@ -4485,28 +4485,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M39">
-        <v>0.9244264999999999</v>
+        <v>0.9494110000000001</v>
       </c>
       <c r="N39">
-        <v>7.525573500000001</v>
+        <v>7.500589000000001</v>
       </c>
       <c r="O39">
-        <v>1.128836025</v>
+        <v>1.12508835</v>
       </c>
       <c r="P39">
-        <v>6.396737475000001</v>
+        <v>6.375500650000001</v>
       </c>
       <c r="Q39">
-        <v>10.746737475</v>
+        <v>10.72550065</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1304753253305067</v>
+        <v>0.131704410979697</v>
       </c>
       <c r="T39">
-        <v>1.014388578705613</v>
+        <v>1.029112708077695</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.140802432643376</v>
+        <v>8.900255000205391</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09893723480741212</v>
+        <v>0.09884926465660497</v>
       </c>
       <c r="C40">
-        <v>30.94961163737671</v>
+        <v>30.50757811384457</v>
       </c>
       <c r="D40">
-        <v>42.62561163737671</v>
+        <v>42.65057811384457</v>
       </c>
       <c r="E40">
-        <v>5.246000000000002</v>
+        <v>5.713000000000001</v>
       </c>
       <c r="F40">
-        <v>17.746</v>
+        <v>18.213</v>
       </c>
       <c r="G40">
         <v>6.07</v>
@@ -4567,28 +4567,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M40">
-        <v>0.9494110000000001</v>
+        <v>0.9743955000000001</v>
       </c>
       <c r="N40">
-        <v>7.500589000000001</v>
+        <v>7.475604500000001</v>
       </c>
       <c r="O40">
-        <v>1.12508835</v>
+        <v>1.121340675</v>
       </c>
       <c r="P40">
-        <v>6.375500650000001</v>
+        <v>6.354263825000001</v>
       </c>
       <c r="Q40">
-        <v>10.72550065</v>
+        <v>10.704263825</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.131704410979697</v>
+        <v>0.1329737945190246</v>
       </c>
       <c r="T40">
-        <v>1.029112708077695</v>
+        <v>1.044319595789846</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.900255000205391</v>
+        <v>8.672043333533459</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09884926465660497</v>
+        <v>0.09876129450579785</v>
       </c>
       <c r="C41">
-        <v>30.50757811384457</v>
+        <v>30.06557385395127</v>
       </c>
       <c r="D41">
-        <v>42.65057811384457</v>
+        <v>42.67557385395127</v>
       </c>
       <c r="E41">
-        <v>5.713000000000001</v>
+        <v>6.180000000000003</v>
       </c>
       <c r="F41">
-        <v>18.213</v>
+        <v>18.68</v>
       </c>
       <c r="G41">
         <v>6.07</v>
@@ -4649,28 +4649,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M41">
-        <v>0.9743955000000001</v>
+        <v>0.9993800000000002</v>
       </c>
       <c r="N41">
-        <v>7.475604500000001</v>
+        <v>7.450620000000001</v>
       </c>
       <c r="O41">
-        <v>1.121340675</v>
+        <v>1.117593</v>
       </c>
       <c r="P41">
-        <v>6.354263825000001</v>
+        <v>6.333027</v>
       </c>
       <c r="Q41">
-        <v>10.704263825</v>
+        <v>10.683027</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1329737945190246</v>
+        <v>0.1342854908429964</v>
       </c>
       <c r="T41">
-        <v>1.044319595789846</v>
+        <v>1.060033379759068</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.672043333533459</v>
+        <v>8.45524225019512</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09876129450579785</v>
+        <v>0.09867332435499074</v>
       </c>
       <c r="C42">
-        <v>30.06557385395127</v>
+        <v>29.62359890917761</v>
       </c>
       <c r="D42">
-        <v>42.67557385395127</v>
+        <v>42.70059890917761</v>
       </c>
       <c r="E42">
-        <v>6.180000000000003</v>
+        <v>6.647000000000002</v>
       </c>
       <c r="F42">
-        <v>18.68</v>
+        <v>19.147</v>
       </c>
       <c r="G42">
         <v>6.07</v>
@@ -4731,28 +4731,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M42">
-        <v>0.9993800000000002</v>
+        <v>1.0243645</v>
       </c>
       <c r="N42">
-        <v>7.450620000000001</v>
+        <v>7.425635500000001</v>
       </c>
       <c r="O42">
-        <v>1.117593</v>
+        <v>1.113845325</v>
       </c>
       <c r="P42">
-        <v>6.333027</v>
+        <v>6.311790175000001</v>
       </c>
       <c r="Q42">
-        <v>10.683027</v>
+        <v>10.661790175</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1342854908429964</v>
+        <v>0.1356416514491368</v>
       </c>
       <c r="T42">
-        <v>1.060033379759068</v>
+        <v>1.076279834371315</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.45524225019512</v>
+        <v>8.249016829458654</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09867332435499074</v>
+        <v>0.0985853542041836</v>
       </c>
       <c r="C43">
-        <v>29.62359890917761</v>
+        <v>29.1816533311252</v>
       </c>
       <c r="D43">
-        <v>42.70059890917761</v>
+        <v>42.72565333112521</v>
       </c>
       <c r="E43">
-        <v>6.647000000000002</v>
+        <v>7.114000000000004</v>
       </c>
       <c r="F43">
-        <v>19.147</v>
+        <v>19.614</v>
       </c>
       <c r="G43">
         <v>6.07</v>
@@ -4813,28 +4813,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M43">
-        <v>1.0243645</v>
+        <v>1.049349</v>
       </c>
       <c r="N43">
-        <v>7.425635500000001</v>
+        <v>7.400651000000001</v>
       </c>
       <c r="O43">
-        <v>1.113845325</v>
+        <v>1.11009765</v>
       </c>
       <c r="P43">
-        <v>6.311790175000001</v>
+        <v>6.290553350000001</v>
       </c>
       <c r="Q43">
-        <v>10.661790175</v>
+        <v>10.64055335</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1356416514491368</v>
+        <v>0.1370445762141097</v>
       </c>
       <c r="T43">
-        <v>1.076279834371315</v>
+        <v>1.093086511556398</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.249016829458654</v>
+        <v>8.052611666852496</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09858535420418363</v>
+        <v>0.09849738405337648</v>
       </c>
       <c r="C44">
-        <v>29.1816533311252</v>
+        <v>28.73973717151687</v>
       </c>
       <c r="D44">
-        <v>42.7256533311252</v>
+        <v>42.75073717151687</v>
       </c>
       <c r="E44">
-        <v>7.114000000000001</v>
+        <v>7.581</v>
       </c>
       <c r="F44">
-        <v>19.614</v>
+        <v>20.081</v>
       </c>
       <c r="G44">
         <v>6.07</v>
@@ -4895,28 +4895,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M44">
-        <v>1.049349</v>
+        <v>1.0743335</v>
       </c>
       <c r="N44">
-        <v>7.400651000000001</v>
+        <v>7.375666500000001</v>
       </c>
       <c r="O44">
-        <v>1.11009765</v>
+        <v>1.106349975</v>
       </c>
       <c r="P44">
-        <v>6.290553350000001</v>
+        <v>6.269316525000001</v>
       </c>
       <c r="Q44">
-        <v>10.64055335</v>
+        <v>10.619316525</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1370445762141097</v>
+        <v>0.1384967264094324</v>
       </c>
       <c r="T44">
-        <v>1.093086511556398</v>
+        <v>1.110482896712887</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.052611666852496</v>
+        <v>7.865341628088485</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09849738405337648</v>
+        <v>0.09840941390256937</v>
       </c>
       <c r="C45">
-        <v>28.73973717151687</v>
+        <v>28.29785048219691</v>
       </c>
       <c r="D45">
-        <v>42.75073717151687</v>
+        <v>42.77585048219692</v>
       </c>
       <c r="E45">
-        <v>7.581</v>
+        <v>8.048000000000002</v>
       </c>
       <c r="F45">
-        <v>20.081</v>
+        <v>20.548</v>
       </c>
       <c r="G45">
         <v>6.07</v>
@@ -4977,28 +4977,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M45">
-        <v>1.0743335</v>
+        <v>1.099318</v>
       </c>
       <c r="N45">
-        <v>7.375666500000001</v>
+        <v>7.350682000000001</v>
       </c>
       <c r="O45">
-        <v>1.106349975</v>
+        <v>1.1026023</v>
       </c>
       <c r="P45">
-        <v>6.269316525000001</v>
+        <v>6.248079700000001</v>
       </c>
       <c r="Q45">
-        <v>10.619316525</v>
+        <v>10.5980797</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1384967264094324</v>
+        <v>0.140000739111731</v>
       </c>
       <c r="T45">
-        <v>1.110482896712887</v>
+        <v>1.128500581339251</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.865341628088485</v>
+        <v>7.686583863813747</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09840941390256937</v>
+        <v>0.09862744375176224</v>
       </c>
       <c r="C46">
-        <v>28.29785048219691</v>
+        <v>27.76866231045219</v>
       </c>
       <c r="D46">
-        <v>42.77585048219692</v>
+        <v>42.71366231045219</v>
       </c>
       <c r="E46">
-        <v>8.048000000000002</v>
+        <v>8.515000000000001</v>
       </c>
       <c r="F46">
-        <v>20.548</v>
+        <v>21.015</v>
       </c>
       <c r="G46">
         <v>6.07</v>
@@ -5059,45 +5059,45 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M46">
-        <v>1.099318</v>
+        <v>1.1411145</v>
       </c>
       <c r="N46">
-        <v>7.350682000000001</v>
+        <v>7.308885500000001</v>
       </c>
       <c r="O46">
-        <v>1.1026023</v>
+        <v>1.096332825</v>
       </c>
       <c r="P46">
-        <v>6.248079700000001</v>
+        <v>6.212552675</v>
       </c>
       <c r="Q46">
-        <v>10.5980797</v>
+        <v>10.562552675</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.140000739111731</v>
+        <v>0.1415594431850223</v>
       </c>
       <c r="T46">
-        <v>1.128500581339251</v>
+        <v>1.147173454497483</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.686583863813747</v>
+        <v>7.40504129953655</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09862744375176224</v>
+        <v>0.09854627360095514</v>
       </c>
       <c r="C47">
-        <v>27.76866231045219</v>
+        <v>27.32479315369978</v>
       </c>
       <c r="D47">
-        <v>42.71366231045219</v>
+        <v>42.73679315369979</v>
       </c>
       <c r="E47">
-        <v>8.515000000000001</v>
+        <v>8.982000000000003</v>
       </c>
       <c r="F47">
-        <v>21.015</v>
+        <v>21.482</v>
       </c>
       <c r="G47">
         <v>6.07</v>
@@ -5141,28 +5141,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M47">
-        <v>1.1411145</v>
+        <v>1.1664726</v>
       </c>
       <c r="N47">
-        <v>7.308885500000001</v>
+        <v>7.283527400000001</v>
       </c>
       <c r="O47">
-        <v>1.096332825</v>
+        <v>1.09252911</v>
       </c>
       <c r="P47">
-        <v>6.212552675</v>
+        <v>6.19099829</v>
       </c>
       <c r="Q47">
-        <v>10.562552675</v>
+        <v>10.54099829</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1415594431850223</v>
+        <v>0.1431758770388058</v>
       </c>
       <c r="T47">
-        <v>1.147173454497483</v>
+        <v>1.166537915550464</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.40504129953655</v>
+        <v>7.244062140850972</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09854627360095514</v>
+        <v>0.098465103450148</v>
       </c>
       <c r="C48">
-        <v>27.32479315369978</v>
+        <v>26.88094906273556</v>
       </c>
       <c r="D48">
-        <v>42.73679315369979</v>
+        <v>42.75994906273556</v>
       </c>
       <c r="E48">
-        <v>8.982000000000003</v>
+        <v>9.449000000000002</v>
       </c>
       <c r="F48">
-        <v>21.482</v>
+        <v>21.949</v>
       </c>
       <c r="G48">
         <v>6.07</v>
@@ -5223,28 +5223,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M48">
-        <v>1.1664726</v>
+        <v>1.1918307</v>
       </c>
       <c r="N48">
-        <v>7.283527400000001</v>
+        <v>7.2581693</v>
       </c>
       <c r="O48">
-        <v>1.09252911</v>
+        <v>1.088725395</v>
       </c>
       <c r="P48">
-        <v>6.19099829</v>
+        <v>6.169443905000001</v>
       </c>
       <c r="Q48">
-        <v>10.54099829</v>
+        <v>10.519443905</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1431758770388058</v>
+        <v>0.1448533083965056</v>
       </c>
       <c r="T48">
-        <v>1.166537915550464</v>
+        <v>1.186633110982803</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.244062140850972</v>
+        <v>7.089933159130739</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.098465103450148</v>
+        <v>0.09838393329934086</v>
       </c>
       <c r="C49">
-        <v>26.88094906273556</v>
+        <v>26.4371300783255</v>
       </c>
       <c r="D49">
-        <v>42.75994906273556</v>
+        <v>42.7831300783255</v>
       </c>
       <c r="E49">
-        <v>9.449000000000002</v>
+        <v>9.916000000000004</v>
       </c>
       <c r="F49">
-        <v>21.949</v>
+        <v>22.416</v>
       </c>
       <c r="G49">
         <v>6.07</v>
@@ -5305,28 +5305,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M49">
-        <v>1.1918307</v>
+        <v>1.2171888</v>
       </c>
       <c r="N49">
-        <v>7.2581693</v>
+        <v>7.2328112</v>
       </c>
       <c r="O49">
-        <v>1.088725395</v>
+        <v>1.08492168</v>
       </c>
       <c r="P49">
-        <v>6.169443905000001</v>
+        <v>6.147889520000001</v>
       </c>
       <c r="Q49">
-        <v>10.519443905</v>
+        <v>10.49788952</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1448533083965056</v>
+        <v>0.1465952563448863</v>
       </c>
       <c r="T49">
-        <v>1.186633110982803</v>
+        <v>1.207501198547155</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.089933159130739</v>
+        <v>6.942226218315515</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09838393329934086</v>
+        <v>0.09830276314853374</v>
       </c>
       <c r="C50">
-        <v>26.4371300783255</v>
+        <v>25.993336241324</v>
       </c>
       <c r="D50">
-        <v>42.7831300783255</v>
+        <v>42.806336241324</v>
       </c>
       <c r="E50">
-        <v>9.916</v>
+        <v>10.383</v>
       </c>
       <c r="F50">
-        <v>22.416</v>
+        <v>22.883</v>
       </c>
       <c r="G50">
         <v>6.07</v>
@@ -5387,28 +5387,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M50">
-        <v>1.2171888</v>
+        <v>1.2425469</v>
       </c>
       <c r="N50">
-        <v>7.232811200000001</v>
+        <v>7.2074531</v>
       </c>
       <c r="O50">
-        <v>1.08492168</v>
+        <v>1.081117965</v>
       </c>
       <c r="P50">
-        <v>6.147889520000001</v>
+        <v>6.126335135000001</v>
       </c>
       <c r="Q50">
-        <v>10.49788952</v>
+        <v>10.476335135</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1465952563448863</v>
+        <v>0.1484055159775171</v>
       </c>
       <c r="T50">
-        <v>1.207501198547155</v>
+        <v>1.229187642486579</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.942226218315517</v>
+        <v>6.800548132227442</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09830276314853374</v>
+        <v>0.09822159299772662</v>
       </c>
       <c r="C51">
-        <v>25.993336241324</v>
+        <v>25.54956759267422</v>
       </c>
       <c r="D51">
-        <v>42.806336241324</v>
+        <v>42.82956759267422</v>
       </c>
       <c r="E51">
-        <v>10.383</v>
+        <v>10.85</v>
       </c>
       <c r="F51">
-        <v>22.883</v>
+        <v>23.35</v>
       </c>
       <c r="G51">
         <v>6.07</v>
@@ -5469,28 +5469,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M51">
-        <v>1.2425469</v>
+        <v>1.267905</v>
       </c>
       <c r="N51">
-        <v>7.2074531</v>
+        <v>7.182095000000001</v>
       </c>
       <c r="O51">
-        <v>1.081117965</v>
+        <v>1.07731425</v>
       </c>
       <c r="P51">
-        <v>6.126335135000001</v>
+        <v>6.104780750000002</v>
       </c>
       <c r="Q51">
-        <v>10.476335135</v>
+        <v>10.45478075</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1484055159775171</v>
+        <v>0.1502881859954532</v>
       </c>
       <c r="T51">
-        <v>1.229187642486579</v>
+        <v>1.251741544183581</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.800548132227442</v>
+        <v>6.664537169582895</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09822159299772662</v>
+        <v>0.0981404228469195</v>
       </c>
       <c r="C52">
-        <v>25.54956759267422</v>
+        <v>25.10582417340817</v>
       </c>
       <c r="D52">
-        <v>42.82956759267422</v>
+        <v>42.85282417340817</v>
       </c>
       <c r="E52">
-        <v>10.85</v>
+        <v>11.317</v>
       </c>
       <c r="F52">
-        <v>23.35</v>
+        <v>23.817</v>
       </c>
       <c r="G52">
         <v>6.07</v>
@@ -5551,28 +5551,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M52">
-        <v>1.267905</v>
+        <v>1.2932631</v>
       </c>
       <c r="N52">
-        <v>7.182095000000001</v>
+        <v>7.156736900000001</v>
       </c>
       <c r="O52">
-        <v>1.07731425</v>
+        <v>1.073510535</v>
       </c>
       <c r="P52">
-        <v>6.104780750000002</v>
+        <v>6.083226365000002</v>
       </c>
       <c r="Q52">
-        <v>10.45478075</v>
+        <v>10.433226365</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1502881859954532</v>
+        <v>0.1522476996875908</v>
       </c>
       <c r="T52">
-        <v>1.251741544183581</v>
+        <v>1.275216013296786</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.664537169582895</v>
+        <v>6.533859970179309</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0981404228469195</v>
+        <v>0.09805925269611238</v>
       </c>
       <c r="C53">
-        <v>25.10582417340817</v>
+        <v>24.66210602464708</v>
       </c>
       <c r="D53">
-        <v>42.85282417340817</v>
+        <v>42.87610602464709</v>
       </c>
       <c r="E53">
-        <v>11.317</v>
+        <v>11.784</v>
       </c>
       <c r="F53">
-        <v>23.817</v>
+        <v>24.284</v>
       </c>
       <c r="G53">
         <v>6.07</v>
@@ -5633,28 +5633,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M53">
-        <v>1.2932631</v>
+        <v>1.3186212</v>
       </c>
       <c r="N53">
-        <v>7.156736900000001</v>
+        <v>7.131378800000001</v>
       </c>
       <c r="O53">
-        <v>1.073510535</v>
+        <v>1.06970682</v>
       </c>
       <c r="P53">
-        <v>6.083226365000002</v>
+        <v>6.061671980000001</v>
       </c>
       <c r="Q53">
-        <v>10.433226365</v>
+        <v>10.41167198</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1522476996875908</v>
+        <v>0.1542888597835675</v>
       </c>
       <c r="T53">
-        <v>1.275216013296786</v>
+        <v>1.299668585289709</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.533859970179309</v>
+        <v>6.40820881690663</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09805925269611238</v>
+        <v>0.09797808254530524</v>
       </c>
       <c r="C54">
-        <v>24.66210602464708</v>
+        <v>24.2184131876016</v>
       </c>
       <c r="D54">
-        <v>42.87610602464709</v>
+        <v>42.8994131876016</v>
       </c>
       <c r="E54">
-        <v>11.784</v>
+        <v>12.251</v>
       </c>
       <c r="F54">
-        <v>24.284</v>
+        <v>24.751</v>
       </c>
       <c r="G54">
         <v>6.07</v>
@@ -5715,28 +5715,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M54">
-        <v>1.3186212</v>
+        <v>1.3439793</v>
       </c>
       <c r="N54">
-        <v>7.131378800000001</v>
+        <v>7.106020700000001</v>
       </c>
       <c r="O54">
-        <v>1.06970682</v>
+        <v>1.065903105</v>
       </c>
       <c r="P54">
-        <v>6.061671980000001</v>
+        <v>6.040117595000001</v>
       </c>
       <c r="Q54">
-        <v>10.41167198</v>
+        <v>10.390117595</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1542888597835675</v>
+        <v>0.1564168777559686</v>
       </c>
       <c r="T54">
-        <v>1.299668585289709</v>
+        <v>1.325161692261054</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.40820881690663</v>
+        <v>6.287299216587638</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09797808254530524</v>
+        <v>0.09789691239449813</v>
       </c>
       <c r="C55">
-        <v>24.2184131876016</v>
+        <v>23.77474570357199</v>
       </c>
       <c r="D55">
-        <v>42.8994131876016</v>
+        <v>42.92274570357199</v>
       </c>
       <c r="E55">
-        <v>12.251</v>
+        <v>12.718</v>
       </c>
       <c r="F55">
-        <v>24.751</v>
+        <v>25.218</v>
       </c>
       <c r="G55">
         <v>6.07</v>
@@ -5797,28 +5797,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M55">
-        <v>1.3439793</v>
+        <v>1.3693374</v>
       </c>
       <c r="N55">
-        <v>7.106020700000001</v>
+        <v>7.080662600000001</v>
       </c>
       <c r="O55">
-        <v>1.065903105</v>
+        <v>1.06209939</v>
       </c>
       <c r="P55">
-        <v>6.040117595000001</v>
+        <v>6.018563210000001</v>
       </c>
       <c r="Q55">
-        <v>10.390117595</v>
+        <v>10.36856321</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1564168777559686</v>
+        <v>0.158637418248909</v>
       </c>
       <c r="T55">
-        <v>1.325161692261054</v>
+        <v>1.351763195187674</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.287299216587638</v>
+        <v>6.170867749613791</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09789691239449813</v>
+        <v>0.098283242243691</v>
       </c>
       <c r="C56">
-        <v>23.77474570357199</v>
+        <v>23.19692093156413</v>
       </c>
       <c r="D56">
-        <v>42.92274570357199</v>
+        <v>42.81192093156413</v>
       </c>
       <c r="E56">
-        <v>12.718</v>
+        <v>13.185</v>
       </c>
       <c r="F56">
-        <v>25.218</v>
+        <v>25.685</v>
       </c>
       <c r="G56">
         <v>6.07</v>
@@ -5879,45 +5879,45 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M56">
-        <v>1.3693374</v>
+        <v>1.4203805</v>
       </c>
       <c r="N56">
-        <v>7.080662600000001</v>
+        <v>7.029619500000001</v>
       </c>
       <c r="O56">
-        <v>1.06209939</v>
+        <v>1.054442925</v>
       </c>
       <c r="P56">
-        <v>6.018563210000001</v>
+        <v>5.975176575000001</v>
       </c>
       <c r="Q56">
-        <v>10.36856321</v>
+        <v>10.325176575</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.158637418248909</v>
+        <v>0.1609566494304245</v>
       </c>
       <c r="T56">
-        <v>1.351763195187674</v>
+        <v>1.379546987133256</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.15</v>
       </c>
       <c r="W56">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.170867749613791</v>
+        <v>5.949110115212085</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.098283242243691</v>
+        <v>0.09821057209288386</v>
       </c>
       <c r="C57">
-        <v>23.19692093156413</v>
+        <v>22.75072378171064</v>
       </c>
       <c r="D57">
-        <v>42.81192093156413</v>
+        <v>42.83272378171065</v>
       </c>
       <c r="E57">
-        <v>13.185</v>
+        <v>13.652</v>
       </c>
       <c r="F57">
-        <v>25.685</v>
+        <v>26.152</v>
       </c>
       <c r="G57">
         <v>6.07</v>
@@ -5961,28 +5961,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M57">
-        <v>1.4203805</v>
+        <v>1.4462056</v>
       </c>
       <c r="N57">
-        <v>7.029619500000001</v>
+        <v>7.0037944</v>
       </c>
       <c r="O57">
-        <v>1.054442925</v>
+        <v>1.05056916</v>
       </c>
       <c r="P57">
-        <v>5.975176575000001</v>
+        <v>5.95322524</v>
       </c>
       <c r="Q57">
-        <v>10.325176575</v>
+        <v>10.30322524</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1609566494304245</v>
+        <v>0.1633813002110997</v>
       </c>
       <c r="T57">
-        <v>1.379546987133256</v>
+        <v>1.408593678712727</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.949110115212085</v>
+        <v>5.842876006011869</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09821057209288386</v>
+        <v>0.09813790194207676</v>
       </c>
       <c r="C58">
-        <v>22.75072378171064</v>
+        <v>22.30454685841788</v>
       </c>
       <c r="D58">
-        <v>42.83272378171065</v>
+        <v>42.85354685841789</v>
       </c>
       <c r="E58">
-        <v>13.652</v>
+        <v>14.119</v>
       </c>
       <c r="F58">
-        <v>26.152</v>
+        <v>26.619</v>
       </c>
       <c r="G58">
         <v>6.07</v>
@@ -6043,28 +6043,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M58">
-        <v>1.4462056</v>
+        <v>1.4720307</v>
       </c>
       <c r="N58">
-        <v>7.0037944</v>
+        <v>6.977969300000001</v>
       </c>
       <c r="O58">
-        <v>1.05056916</v>
+        <v>1.046695395</v>
       </c>
       <c r="P58">
-        <v>5.95322524</v>
+        <v>5.931273905000001</v>
       </c>
       <c r="Q58">
-        <v>10.30322524</v>
+        <v>10.281273905</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1633813002110997</v>
+        <v>0.1659187254466901</v>
       </c>
       <c r="T58">
-        <v>1.408593678712727</v>
+        <v>1.438991379202872</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.842876006011869</v>
+        <v>5.74036940941517</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09813790194207676</v>
+        <v>0.09806523179126964</v>
       </c>
       <c r="C59">
-        <v>22.30454685841788</v>
+        <v>21.85839019119955</v>
       </c>
       <c r="D59">
-        <v>42.85354685841789</v>
+        <v>42.87439019119956</v>
       </c>
       <c r="E59">
-        <v>14.119</v>
+        <v>14.58600000000001</v>
       </c>
       <c r="F59">
-        <v>26.619</v>
+        <v>27.08600000000001</v>
       </c>
       <c r="G59">
         <v>6.07</v>
@@ -6125,28 +6125,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M59">
-        <v>1.4720307</v>
+        <v>1.4978558</v>
       </c>
       <c r="N59">
-        <v>6.977969300000001</v>
+        <v>6.952144200000001</v>
       </c>
       <c r="O59">
-        <v>1.046695395</v>
+        <v>1.04282163</v>
       </c>
       <c r="P59">
-        <v>5.931273905000001</v>
+        <v>5.90932257</v>
       </c>
       <c r="Q59">
-        <v>10.281273905</v>
+        <v>10.25932257</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1659187254466901</v>
+        <v>0.1685769804554039</v>
       </c>
       <c r="T59">
-        <v>1.438991379202872</v>
+        <v>1.470836589240166</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.74036940941517</v>
+        <v>5.641397523045943</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09806523179126962</v>
+        <v>0.09799256164046249</v>
       </c>
       <c r="C60">
-        <v>21.85839019119957</v>
+        <v>21.41225380962682</v>
       </c>
       <c r="D60">
-        <v>42.87439019119957</v>
+        <v>42.89525380962682</v>
       </c>
       <c r="E60">
-        <v>14.586</v>
+        <v>15.053</v>
       </c>
       <c r="F60">
-        <v>27.086</v>
+        <v>27.553</v>
       </c>
       <c r="G60">
         <v>6.07</v>
@@ -6207,28 +6207,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M60">
-        <v>1.4978558</v>
+        <v>1.5236809</v>
       </c>
       <c r="N60">
-        <v>6.952144200000001</v>
+        <v>6.926319100000001</v>
       </c>
       <c r="O60">
-        <v>1.04282163</v>
+        <v>1.038947865</v>
       </c>
       <c r="P60">
-        <v>5.90932257</v>
+        <v>5.887371235000001</v>
       </c>
       <c r="Q60">
-        <v>10.25932257</v>
+        <v>10.237371235</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1685769804554039</v>
+        <v>0.1713649064401524</v>
       </c>
       <c r="T60">
-        <v>1.470836589240166</v>
+        <v>1.504235224157328</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.641397523045944</v>
+        <v>5.545780615875674</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09799256164046249</v>
+        <v>0.09791989148965535</v>
       </c>
       <c r="C61">
-        <v>21.41225380962682</v>
+        <v>20.96613774332839</v>
       </c>
       <c r="D61">
-        <v>42.89525380962682</v>
+        <v>42.91613774332838</v>
       </c>
       <c r="E61">
-        <v>15.053</v>
+        <v>15.52</v>
       </c>
       <c r="F61">
-        <v>27.553</v>
+        <v>28.02</v>
       </c>
       <c r="G61">
         <v>6.07</v>
@@ -6289,28 +6289,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M61">
-        <v>1.5236809</v>
+        <v>1.549506</v>
       </c>
       <c r="N61">
-        <v>6.926319100000001</v>
+        <v>6.900494000000001</v>
       </c>
       <c r="O61">
-        <v>1.038947865</v>
+        <v>1.0350741</v>
       </c>
       <c r="P61">
-        <v>5.887371235000001</v>
+        <v>5.865419900000001</v>
       </c>
       <c r="Q61">
-        <v>10.237371235</v>
+        <v>10.2154199</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1713649064401524</v>
+        <v>0.1742922287241384</v>
       </c>
       <c r="T61">
-        <v>1.504235224157328</v>
+        <v>1.539303790820349</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.545780615875674</v>
+        <v>5.453350938944412</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09791989148965535</v>
+        <v>0.09784722133884827</v>
       </c>
       <c r="C62">
-        <v>20.96613774332839</v>
+        <v>20.52004202199072</v>
       </c>
       <c r="D62">
-        <v>42.91613774332838</v>
+        <v>42.93704202199072</v>
       </c>
       <c r="E62">
-        <v>15.52</v>
+        <v>15.987</v>
       </c>
       <c r="F62">
-        <v>28.02</v>
+        <v>28.487</v>
       </c>
       <c r="G62">
         <v>6.07</v>
@@ -6371,28 +6371,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M62">
-        <v>1.549506</v>
+        <v>1.5753311</v>
       </c>
       <c r="N62">
-        <v>6.900494000000001</v>
+        <v>6.874668900000001</v>
       </c>
       <c r="O62">
-        <v>1.0350741</v>
+        <v>1.031200335</v>
       </c>
       <c r="P62">
-        <v>5.865419900000001</v>
+        <v>5.843468565000001</v>
       </c>
       <c r="Q62">
-        <v>10.2154199</v>
+        <v>10.193468565</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1742922287241384</v>
+        <v>0.1773696700996109</v>
       </c>
       <c r="T62">
-        <v>1.539303790820349</v>
+        <v>1.576170745517371</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.453350938944412</v>
+        <v>5.363951743224012</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09784722133884827</v>
+        <v>0.09777455118804113</v>
       </c>
       <c r="C63">
-        <v>20.52004202199072</v>
+        <v>20.07396667535819</v>
       </c>
       <c r="D63">
-        <v>42.93704202199072</v>
+        <v>42.95796667535819</v>
       </c>
       <c r="E63">
-        <v>15.987</v>
+        <v>16.454</v>
       </c>
       <c r="F63">
-        <v>28.487</v>
+        <v>28.954</v>
       </c>
       <c r="G63">
         <v>6.07</v>
@@ -6453,28 +6453,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M63">
-        <v>1.5753311</v>
+        <v>1.6011562</v>
       </c>
       <c r="N63">
-        <v>6.874668900000001</v>
+        <v>6.848843800000001</v>
       </c>
       <c r="O63">
-        <v>1.031200335</v>
+        <v>1.02732657</v>
       </c>
       <c r="P63">
-        <v>5.843468565000001</v>
+        <v>5.821517230000001</v>
       </c>
       <c r="Q63">
-        <v>10.193468565</v>
+        <v>10.17151723</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1773696700996109</v>
+        <v>0.1806090820737924</v>
       </c>
       <c r="T63">
-        <v>1.576170745517371</v>
+        <v>1.614978066251078</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.363951743224012</v>
+        <v>5.277436392526851</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09777455118804113</v>
+        <v>0.09770188103723401</v>
       </c>
       <c r="C64">
-        <v>20.07396667535819</v>
+        <v>19.62791173323311</v>
       </c>
       <c r="D64">
-        <v>42.95796667535819</v>
+        <v>42.97891173323311</v>
       </c>
       <c r="E64">
-        <v>16.454</v>
+        <v>16.921</v>
       </c>
       <c r="F64">
-        <v>28.954</v>
+        <v>29.421</v>
       </c>
       <c r="G64">
         <v>6.07</v>
@@ -6535,28 +6535,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M64">
-        <v>1.6011562</v>
+        <v>1.6269813</v>
       </c>
       <c r="N64">
-        <v>6.848843800000001</v>
+        <v>6.8230187</v>
       </c>
       <c r="O64">
-        <v>1.02732657</v>
+        <v>1.023452805</v>
       </c>
       <c r="P64">
-        <v>5.821517230000001</v>
+        <v>5.799565895000001</v>
       </c>
       <c r="Q64">
-        <v>10.17151723</v>
+        <v>10.149565895</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1806090820737924</v>
+        <v>0.1840235973979298</v>
       </c>
       <c r="T64">
-        <v>1.614978066251078</v>
+        <v>1.655883079997418</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.277436392526851</v>
+        <v>5.193667560899439</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09770188103723401</v>
+        <v>0.09762921088642688</v>
       </c>
       <c r="C65">
-        <v>19.62791173323311</v>
+        <v>19.181877225476</v>
       </c>
       <c r="D65">
-        <v>42.97891173323311</v>
+        <v>42.999877225476</v>
       </c>
       <c r="E65">
-        <v>16.921</v>
+        <v>17.388</v>
       </c>
       <c r="F65">
-        <v>29.421</v>
+        <v>29.888</v>
       </c>
       <c r="G65">
         <v>6.07</v>
@@ -6617,28 +6617,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M65">
-        <v>1.6269813</v>
+        <v>1.6528064</v>
       </c>
       <c r="N65">
-        <v>6.8230187</v>
+        <v>6.797193600000001</v>
       </c>
       <c r="O65">
-        <v>1.023452805</v>
+        <v>1.01957904</v>
       </c>
       <c r="P65">
-        <v>5.799565895000001</v>
+        <v>5.777614560000001</v>
       </c>
       <c r="Q65">
-        <v>10.149565895</v>
+        <v>10.12761456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1840235973979298</v>
+        <v>0.1876278080178524</v>
       </c>
       <c r="T65">
-        <v>1.655883079997418</v>
+        <v>1.699060594507443</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.193667560899439</v>
+        <v>5.112516505260386</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09762921088642688</v>
+        <v>0.09755654073561976</v>
       </c>
       <c r="C66">
-        <v>19.181877225476</v>
+        <v>18.73586318200563</v>
       </c>
       <c r="D66">
-        <v>42.999877225476</v>
+        <v>43.02086318200563</v>
       </c>
       <c r="E66">
-        <v>17.388</v>
+        <v>17.855</v>
       </c>
       <c r="F66">
-        <v>29.888</v>
+        <v>30.355</v>
       </c>
       <c r="G66">
         <v>6.07</v>
@@ -6699,28 +6699,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M66">
-        <v>1.6528064</v>
+        <v>1.6786315</v>
       </c>
       <c r="N66">
-        <v>6.797193600000001</v>
+        <v>6.771368500000001</v>
       </c>
       <c r="O66">
-        <v>1.01957904</v>
+        <v>1.015705275</v>
       </c>
       <c r="P66">
-        <v>5.777614560000001</v>
+        <v>5.755663225000001</v>
       </c>
       <c r="Q66">
-        <v>10.12761456</v>
+        <v>10.105663225</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1876278080178524</v>
+        <v>0.1914379735303422</v>
       </c>
       <c r="T66">
-        <v>1.699060594507443</v>
+        <v>1.744705395560898</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.112516505260386</v>
+        <v>5.033862405179457</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09755654073561976</v>
+        <v>0.09748387058481264</v>
       </c>
       <c r="C67">
-        <v>18.73586318200563</v>
+        <v>18.28986963279924</v>
       </c>
       <c r="D67">
-        <v>43.02086318200563</v>
+        <v>43.04186963279924</v>
       </c>
       <c r="E67">
-        <v>17.855</v>
+        <v>18.322</v>
       </c>
       <c r="F67">
-        <v>30.355</v>
+        <v>30.822</v>
       </c>
       <c r="G67">
         <v>6.07</v>
@@ -6781,28 +6781,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M67">
-        <v>1.6786315</v>
+        <v>1.7044566</v>
       </c>
       <c r="N67">
-        <v>6.771368500000001</v>
+        <v>6.745543400000001</v>
       </c>
       <c r="O67">
-        <v>1.015705275</v>
+        <v>1.01183151</v>
       </c>
       <c r="P67">
-        <v>5.755663225000001</v>
+        <v>5.73371189</v>
       </c>
       <c r="Q67">
-        <v>10.105663225</v>
+        <v>10.08371189</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1914379735303422</v>
+        <v>0.1954722664259195</v>
       </c>
       <c r="T67">
-        <v>1.744705395560898</v>
+        <v>1.793035184911616</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.033862405179457</v>
+        <v>4.957591762676738</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09748387058481264</v>
+        <v>0.09741120043400552</v>
       </c>
       <c r="C68">
-        <v>18.28986963279924</v>
+        <v>17.84389660789262</v>
       </c>
       <c r="D68">
-        <v>43.04186963279924</v>
+        <v>43.06289660789263</v>
       </c>
       <c r="E68">
-        <v>18.322</v>
+        <v>18.78900000000001</v>
       </c>
       <c r="F68">
-        <v>30.822</v>
+        <v>31.28900000000001</v>
       </c>
       <c r="G68">
         <v>6.07</v>
@@ -6863,28 +6863,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M68">
-        <v>1.7044566</v>
+        <v>1.7302817</v>
       </c>
       <c r="N68">
-        <v>6.745543400000001</v>
+        <v>6.7197183</v>
       </c>
       <c r="O68">
-        <v>1.01183151</v>
+        <v>1.007957745</v>
       </c>
       <c r="P68">
-        <v>5.73371189</v>
+        <v>5.711760555000001</v>
       </c>
       <c r="Q68">
-        <v>10.08371189</v>
+        <v>10.061760555</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1954722664259195</v>
+        <v>0.1997510619212289</v>
       </c>
       <c r="T68">
-        <v>1.793035184911616</v>
+        <v>1.844294052404801</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.957591762676738</v>
+        <v>4.883597855771114</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09741120043400552</v>
+        <v>0.09733853028319839</v>
       </c>
       <c r="C69">
-        <v>17.84389660789262</v>
+        <v>17.39794413738031</v>
       </c>
       <c r="D69">
-        <v>43.06289660789263</v>
+        <v>43.08394413738031</v>
       </c>
       <c r="E69">
-        <v>18.78900000000001</v>
+        <v>19.256</v>
       </c>
       <c r="F69">
-        <v>31.28900000000001</v>
+        <v>31.756</v>
       </c>
       <c r="G69">
         <v>6.07</v>
@@ -6945,28 +6945,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M69">
-        <v>1.7302817</v>
+        <v>1.7561068</v>
       </c>
       <c r="N69">
-        <v>6.7197183</v>
+        <v>6.693893200000001</v>
       </c>
       <c r="O69">
-        <v>1.007957745</v>
+        <v>1.00408398</v>
       </c>
       <c r="P69">
-        <v>5.711760555000001</v>
+        <v>5.689809220000001</v>
       </c>
       <c r="Q69">
-        <v>10.061760555</v>
+        <v>10.03980922</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1997510619212289</v>
+        <v>0.204297282134995</v>
       </c>
       <c r="T69">
-        <v>1.844294052404801</v>
+        <v>1.89875659911631</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.883597855771114</v>
+        <v>4.811780240245069</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09733853028319839</v>
+        <v>0.09726586013239126</v>
       </c>
       <c r="C70">
-        <v>17.39794413738031</v>
+        <v>16.95201225141569</v>
       </c>
       <c r="D70">
-        <v>43.08394413738031</v>
+        <v>43.10501225141569</v>
       </c>
       <c r="E70">
-        <v>19.256</v>
+        <v>19.72300000000001</v>
       </c>
       <c r="F70">
-        <v>31.756</v>
+        <v>32.22300000000001</v>
       </c>
       <c r="G70">
         <v>6.07</v>
@@ -7027,28 +7027,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M70">
-        <v>1.7561068</v>
+        <v>1.7819319</v>
       </c>
       <c r="N70">
-        <v>6.693893200000001</v>
+        <v>6.668068100000001</v>
       </c>
       <c r="O70">
-        <v>1.00408398</v>
+        <v>1.000210215</v>
       </c>
       <c r="P70">
-        <v>5.689809220000001</v>
+        <v>5.667857885000001</v>
       </c>
       <c r="Q70">
-        <v>10.03980922</v>
+        <v>10.017857885</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.204297282134995</v>
+        <v>0.2091368068786815</v>
       </c>
       <c r="T70">
-        <v>1.89875659911631</v>
+        <v>1.956732858518885</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.811780240245069</v>
+        <v>4.742044294734271</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09726586013239126</v>
+        <v>0.09719318998158413</v>
       </c>
       <c r="C71">
-        <v>16.95201225141569</v>
+        <v>16.50610098021115</v>
       </c>
       <c r="D71">
-        <v>43.10501225141569</v>
+        <v>43.12610098021116</v>
       </c>
       <c r="E71">
-        <v>19.72300000000001</v>
+        <v>20.19</v>
       </c>
       <c r="F71">
-        <v>32.22300000000001</v>
+        <v>32.69</v>
       </c>
       <c r="G71">
         <v>6.07</v>
@@ -7109,28 +7109,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M71">
-        <v>1.7819319</v>
+        <v>1.807757</v>
       </c>
       <c r="N71">
-        <v>6.668068100000001</v>
+        <v>6.642243000000001</v>
       </c>
       <c r="O71">
-        <v>1.000210215</v>
+        <v>0.99633645</v>
       </c>
       <c r="P71">
-        <v>5.667857885000001</v>
+        <v>5.64590655</v>
       </c>
       <c r="Q71">
-        <v>10.017857885</v>
+        <v>9.995906550000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2091368068786815</v>
+        <v>0.2142989666052805</v>
       </c>
       <c r="T71">
-        <v>1.956732858518885</v>
+        <v>2.018574201881631</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.742044294734271</v>
+        <v>4.674300804809496</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09719318998158413</v>
+        <v>0.09712051983077702</v>
       </c>
       <c r="C72">
-        <v>16.50610098021115</v>
+        <v>16.06021035403825</v>
       </c>
       <c r="D72">
-        <v>43.12610098021116</v>
+        <v>43.14721035403826</v>
       </c>
       <c r="E72">
-        <v>20.19</v>
+        <v>20.657</v>
       </c>
       <c r="F72">
-        <v>32.69</v>
+        <v>33.157</v>
       </c>
       <c r="G72">
         <v>6.07</v>
@@ -7191,28 +7191,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M72">
-        <v>1.807757</v>
+        <v>1.8335821</v>
       </c>
       <c r="N72">
-        <v>6.642243000000001</v>
+        <v>6.616417900000001</v>
       </c>
       <c r="O72">
-        <v>0.99633645</v>
+        <v>0.9924626850000001</v>
       </c>
       <c r="P72">
-        <v>5.64590655</v>
+        <v>5.623955215000001</v>
       </c>
       <c r="Q72">
-        <v>9.995906550000001</v>
+        <v>9.973955215</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2142989666052805</v>
+        <v>0.219817137347507</v>
       </c>
       <c r="T72">
-        <v>2.018574201881631</v>
+        <v>2.08468046547629</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.674300804809496</v>
+        <v>4.608465582206545</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09712051983077702</v>
+        <v>0.09704784967996988</v>
       </c>
       <c r="C73">
-        <v>16.06021035403825</v>
+        <v>15.61434040322786</v>
       </c>
       <c r="D73">
-        <v>43.14721035403826</v>
+        <v>43.16834040322787</v>
       </c>
       <c r="E73">
-        <v>20.657</v>
+        <v>21.124</v>
       </c>
       <c r="F73">
-        <v>33.157</v>
+        <v>33.624</v>
       </c>
       <c r="G73">
         <v>6.07</v>
@@ -7273,28 +7273,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M73">
-        <v>1.8335821</v>
+        <v>1.8594072</v>
       </c>
       <c r="N73">
-        <v>6.616417900000001</v>
+        <v>6.590592800000001</v>
       </c>
       <c r="O73">
-        <v>0.9924626850000001</v>
+        <v>0.9885889200000002</v>
       </c>
       <c r="P73">
-        <v>5.623955215000001</v>
+        <v>5.602003880000002</v>
       </c>
       <c r="Q73">
-        <v>9.973955215</v>
+        <v>9.952003880000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2198171373475069</v>
+        <v>0.2257294631427496</v>
       </c>
       <c r="T73">
-        <v>2.08468046547629</v>
+        <v>2.155508605041996</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.608465582206545</v>
+        <v>4.54445911578701</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09704784967996988</v>
+        <v>0.09852642952916277</v>
       </c>
       <c r="C74">
-        <v>15.61434040322786</v>
+        <v>14.72145187785245</v>
       </c>
       <c r="D74">
-        <v>43.16834040322787</v>
+        <v>42.74245187785245</v>
       </c>
       <c r="E74">
-        <v>21.124</v>
+        <v>21.591</v>
       </c>
       <c r="F74">
-        <v>33.624</v>
+        <v>34.091</v>
       </c>
       <c r="G74">
         <v>6.07</v>
@@ -7355,45 +7355,45 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M74">
-        <v>1.8594072</v>
+        <v>1.9704598</v>
       </c>
       <c r="N74">
-        <v>6.590592800000001</v>
+        <v>6.479540200000001</v>
       </c>
       <c r="O74">
-        <v>0.9885889200000002</v>
+        <v>0.97193103</v>
       </c>
       <c r="P74">
-        <v>5.602003880000002</v>
+        <v>5.50760917</v>
       </c>
       <c r="Q74">
-        <v>9.952003880000001</v>
+        <v>9.85760917</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2257294631427496</v>
+        <v>0.2320797389968991</v>
       </c>
       <c r="T74">
-        <v>2.155508605041996</v>
+        <v>2.231583273464421</v>
       </c>
       <c r="U74">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V74">
         <v>0.15</v>
       </c>
       <c r="W74">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.54445911578701</v>
+        <v>4.288339198800198</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09852642952916277</v>
+        <v>0.09847500937835564</v>
       </c>
       <c r="C75">
-        <v>14.72145187785245</v>
+        <v>14.26912179335245</v>
       </c>
       <c r="D75">
-        <v>42.74245187785245</v>
+        <v>42.75712179335245</v>
       </c>
       <c r="E75">
-        <v>21.591</v>
+        <v>22.058</v>
       </c>
       <c r="F75">
-        <v>34.091</v>
+        <v>34.558</v>
       </c>
       <c r="G75">
         <v>6.07</v>
@@ -7437,28 +7437,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M75">
-        <v>1.9704598</v>
+        <v>1.9974524</v>
       </c>
       <c r="N75">
-        <v>6.479540200000001</v>
+        <v>6.452547600000001</v>
       </c>
       <c r="O75">
-        <v>0.97193103</v>
+        <v>0.9678821400000001</v>
       </c>
       <c r="P75">
-        <v>5.50760917</v>
+        <v>5.48466546</v>
       </c>
       <c r="Q75">
-        <v>9.85760917</v>
+        <v>9.83466546</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2320797389968991</v>
+        <v>0.2389184976090601</v>
       </c>
       <c r="T75">
-        <v>2.231583273464421</v>
+        <v>2.313509839457803</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.288339198800198</v>
+        <v>4.230388669086683</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09847500937835564</v>
+        <v>0.09842358922754851</v>
       </c>
       <c r="C76">
-        <v>14.26912179335245</v>
+        <v>13.81680178222442</v>
       </c>
       <c r="D76">
-        <v>42.75712179335245</v>
+        <v>42.77180178222442</v>
       </c>
       <c r="E76">
-        <v>22.058</v>
+        <v>22.52500000000001</v>
       </c>
       <c r="F76">
-        <v>34.558</v>
+        <v>35.02500000000001</v>
       </c>
       <c r="G76">
         <v>6.07</v>
@@ -7519,28 +7519,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M76">
-        <v>1.9974524</v>
+        <v>2.024445</v>
       </c>
       <c r="N76">
-        <v>6.452547600000001</v>
+        <v>6.425555000000001</v>
       </c>
       <c r="O76">
-        <v>0.9678821400000001</v>
+        <v>0.9638332500000001</v>
       </c>
       <c r="P76">
-        <v>5.48466546</v>
+        <v>5.461721750000001</v>
       </c>
       <c r="Q76">
-        <v>9.83466546</v>
+        <v>9.81172175</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2389184976090601</v>
+        <v>0.2463043569101941</v>
       </c>
       <c r="T76">
-        <v>2.313509839457803</v>
+        <v>2.401990530730655</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.230388669086683</v>
+        <v>4.173983486832194</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09842358922754851</v>
+        <v>0.0983721690767414</v>
       </c>
       <c r="C77">
-        <v>13.81680178222442</v>
+        <v>13.36449185484754</v>
       </c>
       <c r="D77">
-        <v>42.77180178222442</v>
+        <v>42.78649185484754</v>
       </c>
       <c r="E77">
-        <v>22.52500000000001</v>
+        <v>22.992</v>
       </c>
       <c r="F77">
-        <v>35.02500000000001</v>
+        <v>35.492</v>
       </c>
       <c r="G77">
         <v>6.07</v>
@@ -7601,28 +7601,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M77">
-        <v>2.024445</v>
+        <v>2.0514376</v>
       </c>
       <c r="N77">
-        <v>6.425555000000001</v>
+        <v>6.398562400000001</v>
       </c>
       <c r="O77">
-        <v>0.9638332500000001</v>
+        <v>0.9597843600000001</v>
       </c>
       <c r="P77">
-        <v>5.461721750000001</v>
+        <v>5.438778040000001</v>
       </c>
       <c r="Q77">
-        <v>9.81172175</v>
+        <v>9.78877804</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2463043569101941</v>
+        <v>0.2543057044864225</v>
       </c>
       <c r="T77">
-        <v>2.401990530730655</v>
+        <v>2.497844612942911</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.173983486832194</v>
+        <v>4.119062651479139</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0983721690767414</v>
+        <v>0.09832074892593426</v>
       </c>
       <c r="C78">
-        <v>13.36449185484754</v>
+        <v>12.91219202161525</v>
       </c>
       <c r="D78">
-        <v>42.78649185484754</v>
+        <v>42.80119202161525</v>
       </c>
       <c r="E78">
-        <v>22.992</v>
+        <v>23.459</v>
       </c>
       <c r="F78">
-        <v>35.492</v>
+        <v>35.959</v>
       </c>
       <c r="G78">
         <v>6.07</v>
@@ -7683,28 +7683,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M78">
-        <v>2.0514376</v>
+        <v>2.0784302</v>
       </c>
       <c r="N78">
-        <v>6.398562400000001</v>
+        <v>6.371569800000001</v>
       </c>
       <c r="O78">
-        <v>0.9597843600000001</v>
+        <v>0.9557354700000001</v>
       </c>
       <c r="P78">
-        <v>5.438778040000001</v>
+        <v>5.415834330000001</v>
       </c>
       <c r="Q78">
-        <v>9.78877804</v>
+        <v>9.765834330000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2543057044864225</v>
+        <v>0.2630028214171055</v>
       </c>
       <c r="T78">
-        <v>2.497844612942911</v>
+        <v>2.602033832738841</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.119062651479139</v>
+        <v>4.065568331330059</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09832074892593426</v>
+        <v>0.09826932877512713</v>
       </c>
       <c r="C79">
-        <v>12.91219202161525</v>
+        <v>12.45990229293525</v>
       </c>
       <c r="D79">
-        <v>42.80119202161525</v>
+        <v>42.81590229293525</v>
       </c>
       <c r="E79">
-        <v>23.459</v>
+        <v>23.926</v>
       </c>
       <c r="F79">
-        <v>35.959</v>
+        <v>36.426</v>
       </c>
       <c r="G79">
         <v>6.07</v>
@@ -7765,28 +7765,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M79">
-        <v>2.0784302</v>
+        <v>2.1054228</v>
       </c>
       <c r="N79">
-        <v>6.371569800000001</v>
+        <v>6.344577200000001</v>
       </c>
       <c r="O79">
-        <v>0.9557354700000001</v>
+        <v>0.9516865800000001</v>
       </c>
       <c r="P79">
-        <v>5.415834330000001</v>
+        <v>5.392890620000001</v>
       </c>
       <c r="Q79">
-        <v>9.765834330000001</v>
+        <v>9.742890620000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2630028214171055</v>
+        <v>0.272490585341487</v>
       </c>
       <c r="T79">
-        <v>2.602033832738841</v>
+        <v>2.715694799788948</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.065568331330059</v>
+        <v>4.01344566041557</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09826932877512713</v>
+        <v>0.10056815862432</v>
       </c>
       <c r="C80">
-        <v>12.45990229293525</v>
+        <v>11.34498268211373</v>
       </c>
       <c r="D80">
-        <v>42.81590229293525</v>
+        <v>42.16798268211373</v>
       </c>
       <c r="E80">
-        <v>23.926</v>
+        <v>24.393</v>
       </c>
       <c r="F80">
-        <v>36.426</v>
+        <v>36.893</v>
       </c>
       <c r="G80">
         <v>6.07</v>
@@ -7847,45 +7847,45 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M80">
-        <v>2.1054228</v>
+        <v>2.2615409</v>
       </c>
       <c r="N80">
-        <v>6.344577200000001</v>
+        <v>6.188459100000001</v>
       </c>
       <c r="O80">
-        <v>0.9516865800000001</v>
+        <v>0.9282688650000002</v>
       </c>
       <c r="P80">
-        <v>5.392890620000001</v>
+        <v>5.260190235000001</v>
       </c>
       <c r="Q80">
-        <v>9.742890620000001</v>
+        <v>9.610190235000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.272490585341487</v>
+        <v>0.2828819458300953</v>
       </c>
       <c r="T80">
-        <v>2.715694799788948</v>
+        <v>2.840180620843826</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.15</v>
       </c>
       <c r="W80">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.01344566041557</v>
+        <v>3.73639052912994</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.10056815862432</v>
+        <v>0.1005464884735129</v>
       </c>
       <c r="C81">
-        <v>11.34498268211373</v>
+        <v>10.88399879409979</v>
       </c>
       <c r="D81">
-        <v>42.16798268211373</v>
+        <v>42.17399879409979</v>
       </c>
       <c r="E81">
-        <v>24.393</v>
+        <v>24.86000000000001</v>
       </c>
       <c r="F81">
-        <v>36.893</v>
+        <v>37.36000000000001</v>
       </c>
       <c r="G81">
         <v>6.07</v>
@@ -7929,28 +7929,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M81">
-        <v>2.2615409</v>
+        <v>2.290168</v>
       </c>
       <c r="N81">
-        <v>6.188459100000001</v>
+        <v>6.159832000000001</v>
       </c>
       <c r="O81">
-        <v>0.9282688650000002</v>
+        <v>0.9239748000000001</v>
       </c>
       <c r="P81">
-        <v>5.260190235000001</v>
+        <v>5.235857200000001</v>
       </c>
       <c r="Q81">
-        <v>9.610190235000001</v>
+        <v>9.5858572</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2828819458300953</v>
+        <v>0.2943124423675645</v>
       </c>
       <c r="T81">
-        <v>2.840180620843826</v>
+        <v>2.977115024004192</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.73639052912994</v>
+        <v>3.689685647515815</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1005464884735129</v>
+        <v>0.1005248183227058</v>
       </c>
       <c r="C82">
-        <v>10.88399879409979</v>
+        <v>10.42301662296988</v>
       </c>
       <c r="D82">
-        <v>42.17399879409979</v>
+        <v>42.18001662296988</v>
       </c>
       <c r="E82">
-        <v>24.86000000000001</v>
+        <v>25.32700000000001</v>
       </c>
       <c r="F82">
-        <v>37.36000000000001</v>
+        <v>37.82700000000001</v>
       </c>
       <c r="G82">
         <v>6.07</v>
@@ -8011,28 +8011,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M82">
-        <v>2.290168</v>
+        <v>2.3187951</v>
       </c>
       <c r="N82">
-        <v>6.159832000000001</v>
+        <v>6.1312049</v>
       </c>
       <c r="O82">
-        <v>0.9239748000000001</v>
+        <v>0.919680735</v>
       </c>
       <c r="P82">
-        <v>5.235857200000001</v>
+        <v>5.211524165</v>
       </c>
       <c r="Q82">
-        <v>9.5858572</v>
+        <v>9.561524165</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2943124423675645</v>
+        <v>0.3069461490668726</v>
       </c>
       <c r="T82">
-        <v>2.977115024004192</v>
+        <v>3.12846357486565</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.689685647515815</v>
+        <v>3.644133972855126</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1005248183227058</v>
+        <v>0.1005031481718986</v>
       </c>
       <c r="C83">
-        <v>10.42301662296988</v>
+        <v>9.96203616945904</v>
       </c>
       <c r="D83">
-        <v>42.18001662296988</v>
+        <v>42.18603616945904</v>
       </c>
       <c r="E83">
-        <v>25.32700000000001</v>
+        <v>25.794</v>
       </c>
       <c r="F83">
-        <v>37.82700000000001</v>
+        <v>38.294</v>
       </c>
       <c r="G83">
         <v>6.07</v>
@@ -8093,28 +8093,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M83">
-        <v>2.3187951</v>
+        <v>2.3474222</v>
       </c>
       <c r="N83">
-        <v>6.1312049</v>
+        <v>6.102577800000001</v>
       </c>
       <c r="O83">
-        <v>0.919680735</v>
+        <v>0.9153866700000001</v>
       </c>
       <c r="P83">
-        <v>5.211524165</v>
+        <v>5.18719113</v>
       </c>
       <c r="Q83">
-        <v>9.561524165</v>
+        <v>9.53719113</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3069461490668726</v>
+        <v>0.3209836009549926</v>
       </c>
       <c r="T83">
-        <v>3.12846357486565</v>
+        <v>3.29662863137838</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.644133972855126</v>
+        <v>3.599693314649576</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1005031481718986</v>
+        <v>0.1004814780210915</v>
       </c>
       <c r="C84">
-        <v>9.96203616945904</v>
+        <v>9.501057434302751</v>
       </c>
       <c r="D84">
-        <v>42.18603616945904</v>
+        <v>42.19205743430275</v>
       </c>
       <c r="E84">
-        <v>25.794</v>
+        <v>26.261</v>
       </c>
       <c r="F84">
-        <v>38.294</v>
+        <v>38.761</v>
       </c>
       <c r="G84">
         <v>6.07</v>
@@ -8175,28 +8175,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M84">
-        <v>2.3474222</v>
+        <v>2.3760493</v>
       </c>
       <c r="N84">
-        <v>6.102577800000001</v>
+        <v>6.073950700000001</v>
       </c>
       <c r="O84">
-        <v>0.9153866700000001</v>
+        <v>0.9110926050000001</v>
       </c>
       <c r="P84">
-        <v>5.18719113</v>
+        <v>5.162858095000001</v>
       </c>
       <c r="Q84">
-        <v>9.53719113</v>
+        <v>9.512858095</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3209836009549926</v>
+        <v>0.3366725177711267</v>
       </c>
       <c r="T84">
-        <v>3.29662863137838</v>
+        <v>3.484577812186726</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.599693314649576</v>
+        <v>3.556323515677895</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1004814780210915</v>
+        <v>0.1004598078702844</v>
       </c>
       <c r="C85">
-        <v>9.501057434302751</v>
+        <v>9.040080418236911</v>
       </c>
       <c r="D85">
-        <v>42.19205743430275</v>
+        <v>42.19808041823692</v>
       </c>
       <c r="E85">
-        <v>26.261</v>
+        <v>26.72800000000001</v>
       </c>
       <c r="F85">
-        <v>38.761</v>
+        <v>39.22800000000001</v>
       </c>
       <c r="G85">
         <v>6.07</v>
@@ -8257,28 +8257,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M85">
-        <v>2.3760493</v>
+        <v>2.4046764</v>
       </c>
       <c r="N85">
-        <v>6.073950700000001</v>
+        <v>6.045323600000001</v>
       </c>
       <c r="O85">
-        <v>0.9110926050000001</v>
+        <v>0.90679854</v>
       </c>
       <c r="P85">
-        <v>5.162858095000001</v>
+        <v>5.138525060000001</v>
       </c>
       <c r="Q85">
-        <v>9.512858095</v>
+        <v>9.488525060000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3366725177711267</v>
+        <v>0.3543225491892776</v>
       </c>
       <c r="T85">
-        <v>3.484577812186726</v>
+        <v>3.696020640596116</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.556323515677895</v>
+        <v>3.513986330967443</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1004598078702844</v>
+        <v>0.1024611377194773</v>
       </c>
       <c r="C86">
-        <v>9.040080418236911</v>
+        <v>8.023992060151841</v>
       </c>
       <c r="D86">
-        <v>42.19808041823691</v>
+        <v>41.64899206015184</v>
       </c>
       <c r="E86">
-        <v>26.728</v>
+        <v>27.195</v>
       </c>
       <c r="F86">
-        <v>39.228</v>
+        <v>39.695</v>
       </c>
       <c r="G86">
         <v>6.07</v>
@@ -8339,45 +8339,45 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M86">
-        <v>2.4046764</v>
+        <v>2.5444495</v>
       </c>
       <c r="N86">
-        <v>6.045323600000001</v>
+        <v>5.9055505</v>
       </c>
       <c r="O86">
-        <v>0.9067985400000002</v>
+        <v>0.885832575</v>
       </c>
       <c r="P86">
-        <v>5.138525060000001</v>
+        <v>5.019717925</v>
       </c>
       <c r="Q86">
-        <v>9.488525060000001</v>
+        <v>9.369717925</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3543225491892774</v>
+        <v>0.3743259181298484</v>
       </c>
       <c r="T86">
-        <v>3.696020640596113</v>
+        <v>3.935655846126754</v>
       </c>
       <c r="U86">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V86">
         <v>0.15</v>
       </c>
       <c r="W86">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.513986330967444</v>
+        <v>3.320954100287705</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1024611377194773</v>
+        <v>0.1024632675686701</v>
       </c>
       <c r="C87">
-        <v>8.023992060151841</v>
+        <v>7.55641532263553</v>
       </c>
       <c r="D87">
-        <v>41.64899206015184</v>
+        <v>41.64841532263553</v>
       </c>
       <c r="E87">
-        <v>27.195</v>
+        <v>27.662</v>
       </c>
       <c r="F87">
-        <v>39.695</v>
+        <v>40.162</v>
       </c>
       <c r="G87">
         <v>6.07</v>
@@ -8421,28 +8421,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M87">
-        <v>2.5444495</v>
+        <v>2.5743842</v>
       </c>
       <c r="N87">
-        <v>5.9055505</v>
+        <v>5.875615800000001</v>
       </c>
       <c r="O87">
-        <v>0.885832575</v>
+        <v>0.8813423700000002</v>
       </c>
       <c r="P87">
-        <v>5.019717925</v>
+        <v>4.994273430000001</v>
       </c>
       <c r="Q87">
-        <v>9.369717925</v>
+        <v>9.344273430000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3743259181298484</v>
+        <v>0.3971869112047867</v>
       </c>
       <c r="T87">
-        <v>3.935655846126754</v>
+        <v>4.209524652447485</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.320954100287705</v>
+        <v>3.282338354935523</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1024632675686701</v>
+        <v>0.102465397417863</v>
       </c>
       <c r="C88">
-        <v>7.55641532263553</v>
+        <v>7.088838601091823</v>
       </c>
       <c r="D88">
-        <v>41.64841532263553</v>
+        <v>41.64783860109183</v>
       </c>
       <c r="E88">
-        <v>27.662</v>
+        <v>28.129</v>
       </c>
       <c r="F88">
-        <v>40.162</v>
+        <v>40.629</v>
       </c>
       <c r="G88">
         <v>6.07</v>
@@ -8503,28 +8503,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M88">
-        <v>2.5743842</v>
+        <v>2.6043189</v>
       </c>
       <c r="N88">
-        <v>5.875615800000001</v>
+        <v>5.8456811</v>
       </c>
       <c r="O88">
-        <v>0.8813423700000002</v>
+        <v>0.876852165</v>
       </c>
       <c r="P88">
-        <v>4.994273430000001</v>
+        <v>4.968828935</v>
       </c>
       <c r="Q88">
-        <v>9.344273430000001</v>
+        <v>9.318828934999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3971869112047867</v>
+        <v>0.4235649801374078</v>
       </c>
       <c r="T88">
-        <v>4.209524652447485</v>
+        <v>4.525527121279099</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.282338354935523</v>
+        <v>3.244610327867298</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.102465397417863</v>
+        <v>0.1024675272670559</v>
       </c>
       <c r="C89">
-        <v>7.088838601091823</v>
+        <v>6.621261895520071</v>
       </c>
       <c r="D89">
-        <v>41.64783860109183</v>
+        <v>41.64726189552007</v>
       </c>
       <c r="E89">
-        <v>28.129</v>
+        <v>28.596</v>
       </c>
       <c r="F89">
-        <v>40.629</v>
+        <v>41.096</v>
       </c>
       <c r="G89">
         <v>6.07</v>
@@ -8585,28 +8585,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M89">
-        <v>2.6043189</v>
+        <v>2.634253600000001</v>
       </c>
       <c r="N89">
-        <v>5.8456811</v>
+        <v>5.8157464</v>
       </c>
       <c r="O89">
-        <v>0.876852165</v>
+        <v>0.87236196</v>
       </c>
       <c r="P89">
-        <v>4.968828935</v>
+        <v>4.94338444</v>
       </c>
       <c r="Q89">
-        <v>9.318828934999999</v>
+        <v>9.293384440000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4235649801374078</v>
+        <v>0.4543393938921325</v>
       </c>
       <c r="T89">
-        <v>4.525527121279099</v>
+        <v>4.894196668249315</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.244610327867298</v>
+        <v>3.207739755959715</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1024675272670559</v>
+        <v>0.1024696571162488</v>
       </c>
       <c r="C90">
-        <v>6.621261895520071</v>
+        <v>6.153685205919608</v>
       </c>
       <c r="D90">
-        <v>41.64726189552007</v>
+        <v>41.64668520591961</v>
       </c>
       <c r="E90">
-        <v>28.596</v>
+        <v>29.063</v>
       </c>
       <c r="F90">
-        <v>41.096</v>
+        <v>41.563</v>
       </c>
       <c r="G90">
         <v>6.07</v>
@@ -8667,28 +8667,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M90">
-        <v>2.634253600000001</v>
+        <v>2.6641883</v>
       </c>
       <c r="N90">
-        <v>5.8157464</v>
+        <v>5.785811700000001</v>
       </c>
       <c r="O90">
-        <v>0.87236196</v>
+        <v>0.8678717550000001</v>
       </c>
       <c r="P90">
-        <v>4.94338444</v>
+        <v>4.917939945000001</v>
       </c>
       <c r="Q90">
-        <v>9.293384440000001</v>
+        <v>9.267939945</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4543393938921325</v>
+        <v>0.4907091556022616</v>
       </c>
       <c r="T90">
-        <v>4.894196668249315</v>
+        <v>5.32989704194139</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.207739755959715</v>
+        <v>3.17169773622983</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1024696571162488</v>
+        <v>0.1024717869654417</v>
       </c>
       <c r="C91">
-        <v>6.153685205919608</v>
+        <v>5.686108532289758</v>
       </c>
       <c r="D91">
-        <v>41.64668520591961</v>
+        <v>41.64610853228976</v>
       </c>
       <c r="E91">
-        <v>29.063</v>
+        <v>29.53</v>
       </c>
       <c r="F91">
-        <v>41.563</v>
+        <v>42.03</v>
       </c>
       <c r="G91">
         <v>6.07</v>
@@ -8749,28 +8749,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M91">
-        <v>2.6641883</v>
+        <v>2.694123</v>
       </c>
       <c r="N91">
-        <v>5.785811700000001</v>
+        <v>5.755877000000001</v>
       </c>
       <c r="O91">
-        <v>0.8678717550000001</v>
+        <v>0.8633815500000001</v>
       </c>
       <c r="P91">
-        <v>4.917939945000001</v>
+        <v>4.892495450000001</v>
       </c>
       <c r="Q91">
-        <v>9.267939945</v>
+        <v>9.24249545</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4907091556022616</v>
+        <v>0.5343528696544166</v>
       </c>
       <c r="T91">
-        <v>5.32989704194139</v>
+        <v>5.852737490371879</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.17169773622983</v>
+        <v>3.136456650271721</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1024717869654417</v>
+        <v>0.1024739168146345</v>
       </c>
       <c r="C92">
-        <v>5.686108532289758</v>
+        <v>5.218531874629853</v>
       </c>
       <c r="D92">
-        <v>41.64610853228976</v>
+        <v>41.64553187462986</v>
       </c>
       <c r="E92">
-        <v>29.53</v>
+        <v>29.99700000000001</v>
       </c>
       <c r="F92">
-        <v>42.03</v>
+        <v>42.49700000000001</v>
       </c>
       <c r="G92">
         <v>6.07</v>
@@ -8831,28 +8831,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M92">
-        <v>2.694123</v>
+        <v>2.724057700000001</v>
       </c>
       <c r="N92">
-        <v>5.755877000000001</v>
+        <v>5.7259423</v>
       </c>
       <c r="O92">
-        <v>0.8633815500000001</v>
+        <v>0.858891345</v>
       </c>
       <c r="P92">
-        <v>4.892495450000001</v>
+        <v>4.867050955</v>
       </c>
       <c r="Q92">
-        <v>9.24249545</v>
+        <v>9.217050954999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5343528696544166</v>
+        <v>0.5876951868292726</v>
       </c>
       <c r="T92">
-        <v>5.852737490371879</v>
+        <v>6.491764705120254</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.136456650271721</v>
+        <v>3.101990093675328</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1024739168146345</v>
+        <v>0.1024760466638274</v>
       </c>
       <c r="C93">
-        <v>5.218531874629853</v>
+        <v>4.750955232939255</v>
       </c>
       <c r="D93">
-        <v>41.64553187462986</v>
+        <v>41.64495523293926</v>
       </c>
       <c r="E93">
-        <v>29.99700000000001</v>
+        <v>30.46400000000001</v>
       </c>
       <c r="F93">
-        <v>42.49700000000001</v>
+        <v>42.96400000000001</v>
       </c>
       <c r="G93">
         <v>6.07</v>
@@ -8913,28 +8913,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M93">
-        <v>2.724057700000001</v>
+        <v>2.7539924</v>
       </c>
       <c r="N93">
-        <v>5.7259423</v>
+        <v>5.696007600000001</v>
       </c>
       <c r="O93">
-        <v>0.858891345</v>
+        <v>0.8544011400000001</v>
       </c>
       <c r="P93">
-        <v>4.867050955</v>
+        <v>4.84160646</v>
       </c>
       <c r="Q93">
-        <v>9.217050954999999</v>
+        <v>9.191606459999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5876951868292726</v>
+        <v>0.6543730832978428</v>
       </c>
       <c r="T93">
-        <v>6.491764705120254</v>
+        <v>7.290548723555724</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.101990093675328</v>
+        <v>3.068272810048423</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1024760466638274</v>
+        <v>0.1024781765130203</v>
       </c>
       <c r="C94">
-        <v>4.750955232939255</v>
+        <v>4.28337860721728</v>
       </c>
       <c r="D94">
-        <v>41.64495523293926</v>
+        <v>41.64437860721728</v>
       </c>
       <c r="E94">
-        <v>30.46400000000001</v>
+        <v>30.931</v>
       </c>
       <c r="F94">
-        <v>42.96400000000001</v>
+        <v>43.431</v>
       </c>
       <c r="G94">
         <v>6.07</v>
@@ -8995,28 +8995,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M94">
-        <v>2.7539924</v>
+        <v>2.783927100000001</v>
       </c>
       <c r="N94">
-        <v>5.696007600000001</v>
+        <v>5.666072900000001</v>
       </c>
       <c r="O94">
-        <v>0.8544011400000001</v>
+        <v>0.849910935</v>
       </c>
       <c r="P94">
-        <v>4.84160646</v>
+        <v>4.816161965000001</v>
       </c>
       <c r="Q94">
-        <v>9.191606459999999</v>
+        <v>9.166161965000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6543730832978428</v>
+        <v>0.7401018073288615</v>
       </c>
       <c r="T94">
-        <v>7.290548723555724</v>
+        <v>8.317556747258472</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.068272810048423</v>
+        <v>3.035280629295214</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1024781765130203</v>
+        <v>0.1024803063622131</v>
       </c>
       <c r="C95">
-        <v>4.28337860721728</v>
+        <v>3.815801997463282</v>
       </c>
       <c r="D95">
-        <v>41.64437860721728</v>
+        <v>41.64380199746329</v>
       </c>
       <c r="E95">
-        <v>30.931</v>
+        <v>31.398</v>
       </c>
       <c r="F95">
-        <v>43.431</v>
+        <v>43.898</v>
       </c>
       <c r="G95">
         <v>6.07</v>
@@ -9077,28 +9077,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M95">
-        <v>2.783927100000001</v>
+        <v>2.8138618</v>
       </c>
       <c r="N95">
-        <v>5.666072900000001</v>
+        <v>5.636138200000001</v>
       </c>
       <c r="O95">
-        <v>0.849910935</v>
+        <v>0.8454207300000002</v>
       </c>
       <c r="P95">
-        <v>4.816161965000001</v>
+        <v>4.790717470000001</v>
       </c>
       <c r="Q95">
-        <v>9.166161965000001</v>
+        <v>9.140717470000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7401018073288615</v>
+        <v>0.8544067727035533</v>
       </c>
       <c r="T95">
-        <v>8.317556747258472</v>
+        <v>9.686900778862134</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.035280629295214</v>
+        <v>3.002990409834627</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1024803063622131</v>
+        <v>0.108780936211406</v>
       </c>
       <c r="C96">
-        <v>3.815801997463282</v>
+        <v>1.710186671738221</v>
       </c>
       <c r="D96">
-        <v>41.64380199746329</v>
+        <v>40.00518667173823</v>
       </c>
       <c r="E96">
-        <v>31.398</v>
+        <v>31.86500000000001</v>
       </c>
       <c r="F96">
-        <v>43.898</v>
+        <v>44.36500000000001</v>
       </c>
       <c r="G96">
         <v>6.07</v>
@@ -9159,45 +9159,45 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M96">
-        <v>2.8138618</v>
+        <v>3.189843500000001</v>
       </c>
       <c r="N96">
-        <v>5.636138200000001</v>
+        <v>5.260156500000001</v>
       </c>
       <c r="O96">
-        <v>0.8454207300000002</v>
+        <v>0.7890234750000001</v>
       </c>
       <c r="P96">
-        <v>4.790717470000001</v>
+        <v>4.471133025</v>
       </c>
       <c r="Q96">
-        <v>9.140717470000002</v>
+        <v>8.821133025</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8544067727035533</v>
+        <v>1.014433724228122</v>
       </c>
       <c r="T96">
-        <v>9.686900778862134</v>
+        <v>11.60398242310727</v>
       </c>
       <c r="U96">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V96">
         <v>0.15</v>
       </c>
       <c r="W96">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.002990409834627</v>
+        <v>2.649032781702299</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.108780936211406</v>
+        <v>0.1088493660605989</v>
       </c>
       <c r="C97">
-        <v>1.710186671738221</v>
+        <v>1.22609757928646</v>
       </c>
       <c r="D97">
-        <v>40.00518667173823</v>
+        <v>39.98809757928647</v>
       </c>
       <c r="E97">
-        <v>31.86500000000001</v>
+        <v>32.33200000000001</v>
       </c>
       <c r="F97">
-        <v>44.36500000000001</v>
+        <v>44.83200000000001</v>
       </c>
       <c r="G97">
         <v>6.07</v>
@@ -9241,28 +9241,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M97">
-        <v>3.189843500000001</v>
+        <v>3.223420800000001</v>
       </c>
       <c r="N97">
-        <v>5.260156500000001</v>
+        <v>5.2265792</v>
       </c>
       <c r="O97">
-        <v>0.7890234750000001</v>
+        <v>0.7839868799999999</v>
       </c>
       <c r="P97">
-        <v>4.471133025</v>
+        <v>4.44259232</v>
       </c>
       <c r="Q97">
-        <v>8.821133025</v>
+        <v>8.792592320000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.014433724228122</v>
+        <v>1.254474151514975</v>
       </c>
       <c r="T97">
-        <v>11.60398242310727</v>
+        <v>14.47960488947496</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.649032781702299</v>
+        <v>2.621438690226234</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1088493660605989</v>
+        <v>0.1089177959097918</v>
       </c>
       <c r="C98">
-        <v>1.226097579286467</v>
+        <v>0.7420230805615802</v>
       </c>
       <c r="D98">
-        <v>39.98809757928647</v>
+        <v>39.97102308056158</v>
       </c>
       <c r="E98">
-        <v>32.332</v>
+        <v>32.799</v>
       </c>
       <c r="F98">
-        <v>44.832</v>
+        <v>45.299</v>
       </c>
       <c r="G98">
         <v>6.07</v>
@@ -9323,28 +9323,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M98">
-        <v>3.2234208</v>
+        <v>3.2569981</v>
       </c>
       <c r="N98">
-        <v>5.226579200000001</v>
+        <v>5.193001900000001</v>
       </c>
       <c r="O98">
-        <v>0.7839868800000001</v>
+        <v>0.7789502850000001</v>
       </c>
       <c r="P98">
-        <v>4.442592320000001</v>
+        <v>4.414051615</v>
       </c>
       <c r="Q98">
-        <v>8.792592320000001</v>
+        <v>8.764051615</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.254474151514972</v>
+        <v>1.654541530326391</v>
       </c>
       <c r="T98">
-        <v>14.47960488947492</v>
+        <v>19.27230900008773</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.621438690226234</v>
+        <v>2.594413549089881</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1089177959097918</v>
+        <v>0.1089862257589847</v>
       </c>
       <c r="C99">
-        <v>0.7420230805615802</v>
+        <v>0.2579631568774445</v>
       </c>
       <c r="D99">
-        <v>39.97102308056158</v>
+        <v>39.95396315687745</v>
       </c>
       <c r="E99">
-        <v>32.799</v>
+        <v>33.26600000000001</v>
       </c>
       <c r="F99">
-        <v>45.299</v>
+        <v>45.76600000000001</v>
       </c>
       <c r="G99">
         <v>6.07</v>
@@ -9405,28 +9405,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M99">
-        <v>3.2569981</v>
+        <v>3.290575400000001</v>
       </c>
       <c r="N99">
-        <v>5.193001900000001</v>
+        <v>5.1594246</v>
       </c>
       <c r="O99">
-        <v>0.7789502850000001</v>
+        <v>0.77391369</v>
       </c>
       <c r="P99">
-        <v>4.414051615</v>
+        <v>4.385510910000001</v>
       </c>
       <c r="Q99">
-        <v>8.764051615</v>
+        <v>8.73551091</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.654541530326391</v>
+        <v>2.454676287949231</v>
       </c>
       <c r="T99">
-        <v>19.27230900008773</v>
+        <v>28.85771722131334</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.594413549089881</v>
+        <v>2.567939941446107</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1089862257589847</v>
+        <v>0.1090546556081775</v>
       </c>
       <c r="C100">
-        <v>0.2579631568774445</v>
+        <v>-0.2260822104201665</v>
       </c>
       <c r="D100">
-        <v>39.95396315687745</v>
+        <v>39.93691778957984</v>
       </c>
       <c r="E100">
-        <v>33.26600000000001</v>
+        <v>33.733</v>
       </c>
       <c r="F100">
-        <v>45.76600000000001</v>
+        <v>46.233</v>
       </c>
       <c r="G100">
         <v>6.07</v>
@@ -9487,28 +9487,28 @@
         <v>8.450000000000001</v>
       </c>
       <c r="M100">
-        <v>3.290575400000001</v>
+        <v>3.3241527</v>
       </c>
       <c r="N100">
-        <v>5.1594246</v>
+        <v>5.1258473</v>
       </c>
       <c r="O100">
-        <v>0.77391369</v>
+        <v>0.768877095</v>
       </c>
       <c r="P100">
-        <v>4.385510910000001</v>
+        <v>4.356970205000001</v>
       </c>
       <c r="Q100">
-        <v>8.73551091</v>
+        <v>8.706970205000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.454676287949231</v>
+        <v>4.855080560817749</v>
       </c>
       <c r="T100">
-        <v>28.85771722131334</v>
+        <v>57.61394188499016</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.567939941446107</v>
+        <v>2.542001154158772</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1090546556081775</v>
-      </c>
-      <c r="C101">
-        <v>-0.2260822104201665</v>
-      </c>
-      <c r="D101">
-        <v>39.93691778957984</v>
-      </c>
-      <c r="E101">
-        <v>33.733</v>
-      </c>
-      <c r="F101">
-        <v>46.233</v>
-      </c>
-      <c r="G101">
-        <v>6.07</v>
-      </c>
-      <c r="H101">
-        <v>34.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.8</v>
-      </c>
-      <c r="K101">
-        <v>4.35</v>
-      </c>
-      <c r="L101">
-        <v>8.450000000000001</v>
-      </c>
-      <c r="M101">
-        <v>3.3241527</v>
-      </c>
-      <c r="N101">
-        <v>5.1258473</v>
-      </c>
-      <c r="O101">
-        <v>0.768877095</v>
-      </c>
-      <c r="P101">
-        <v>4.356970205000001</v>
-      </c>
-      <c r="Q101">
-        <v>8.706970205000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.855080560817749</v>
-      </c>
-      <c r="T101">
-        <v>57.61394188499016</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.061115</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.542001154158772</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
